--- a/SG_Arese_2025_26_Analisi.xlsx
+++ b/SG_Arese_2025_26_Analisi.xlsx
@@ -1520,7 +1520,7 @@
     <t>Indice normalizzato 0-100 calcolato separatamente per giocatori di movimento e portieri, a partire dalla valutazione grezza totale stagionale.</t>
   </si>
   <si>
-    <t>5*gol + 3*assist + 1*tiri + 2*palla_rubata + 2*et_pos + 1*tr_pos + 3*parata - 2*et_neg - 1*tr_neg - 2*palla_persa - 1*gol_subito - 2*controfallo - 2*errore</t>
+    <t>5*gol + 3*assist + 0.5*tiri + 2*palla_rubata + 2.5*et_pos + 3*tr_pos + 1*parata - 2.5*et_neg - 3*tr_neg - 2*palla_persa - 1*gol_subito - 2*controfallo - 2*errore</t>
   </si>
   <si>
     <t>3*parata + 3*assist + 5*gol + 2*palla_rubata - 3*gol_subito - 2*et_neg - 1*tr_neg - 2*palla_persa - 2*controfallo - 2*errore</t>
@@ -2226,10 +2226,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>32.44333333333334</c:v>
+                  <c:v>36.082</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>40.36</c:v>
+                  <c:v>45.18</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2379,10 +2379,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>59.2</c:v>
+                  <c:v>65.48999999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>24.18416666666667</c:v>
+                  <c:v>27.0375</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5048,10 +5048,10 @@
               <c:strCache>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>ZENO</c:v>
+                  <c:v>BOBBY</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>BOBBY</c:v>
+                  <c:v>ZENO</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>CRIVE A.</c:v>
@@ -5084,25 +5084,25 @@
                   <c:v>100</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>96.44</c:v>
+                  <c:v>98.39</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>59.05</c:v>
+                  <c:v>73.20999999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>49.85</c:v>
+                  <c:v>62.32</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>41.25</c:v>
+                  <c:v>45.36</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>40.36</c:v>
+                  <c:v>45.18</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>40.06</c:v>
+                  <c:v>43.39</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>29.67</c:v>
+                  <c:v>33.39</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5276,16 +5276,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>21.364</c:v>
+                  <c:v>24.82</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>16.71666666666667</c:v>
+                  <c:v>17.38</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>51.634</c:v>
+                  <c:v>53.536</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>37.29</c:v>
+                  <c:v>47.49666666666666</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8560,19 +8560,19 @@
         <v>14</v>
       </c>
       <c r="AQ2">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="AR2">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="AS2" s="18">
-        <v>9.857143000000001</v>
+        <v>8.357143000000001</v>
       </c>
       <c r="AT2" s="18">
-        <v>9.857143000000001</v>
+        <v>8.357143000000001</v>
       </c>
       <c r="AU2">
-        <v>41.25</v>
+        <v>45.36</v>
       </c>
     </row>
     <row r="3" spans="1:47">
@@ -8694,19 +8694,19 @@
         <v>16</v>
       </c>
       <c r="AQ3">
-        <v>33</v>
+        <v>5.5</v>
       </c>
       <c r="AR3">
-        <v>33</v>
+        <v>5.5</v>
       </c>
       <c r="AS3" s="18">
-        <v>2.0625</v>
+        <v>0.34375</v>
       </c>
       <c r="AT3" s="18">
-        <v>2.0625</v>
+        <v>0.34375</v>
       </c>
       <c r="AU3">
-        <v>10.09</v>
+        <v>5.54</v>
       </c>
     </row>
     <row r="4" spans="1:47">
@@ -8834,19 +8834,19 @@
         <v>16</v>
       </c>
       <c r="AQ4">
-        <v>324</v>
+        <v>270</v>
       </c>
       <c r="AR4">
-        <v>324</v>
+        <v>270</v>
       </c>
       <c r="AS4" s="18">
-        <v>20.25</v>
+        <v>16.875</v>
       </c>
       <c r="AT4" s="18">
-        <v>20.25</v>
+        <v>16.875</v>
       </c>
       <c r="AU4">
-        <v>96.44</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:47">
@@ -8965,19 +8965,19 @@
         <v>1</v>
       </c>
       <c r="AQ5">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="AR5">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="AS5" s="18">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="AT5" s="18">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="AU5">
-        <v>2.97</v>
+        <v>6.96</v>
       </c>
     </row>
     <row r="6" spans="1:47">
@@ -9105,19 +9105,19 @@
         <v>15</v>
       </c>
       <c r="AQ6">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="AR6">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="AS6" s="18">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="AT6" s="18">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="AU6">
-        <v>59.05</v>
+        <v>73.20999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:47">
@@ -9239,19 +9239,19 @@
         <v>16</v>
       </c>
       <c r="AQ7">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="AR7">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="AS7" s="18">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="AT7" s="18">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="AU7">
-        <v>20.47</v>
+        <v>23.57</v>
       </c>
     </row>
     <row r="8" spans="1:47">
@@ -9373,19 +9373,19 @@
         <v>15</v>
       </c>
       <c r="AQ8">
-        <v>135</v>
+        <v>116.5</v>
       </c>
       <c r="AR8">
-        <v>135</v>
+        <v>116.5</v>
       </c>
       <c r="AS8" s="18">
-        <v>9</v>
+        <v>7.766667</v>
       </c>
       <c r="AT8" s="18">
-        <v>9</v>
+        <v>7.766667</v>
       </c>
       <c r="AU8">
-        <v>40.36</v>
+        <v>45.18</v>
       </c>
     </row>
     <row r="9" spans="1:47">
@@ -9513,19 +9513,19 @@
         <v>15</v>
       </c>
       <c r="AQ9">
-        <v>134</v>
+        <v>111.5</v>
       </c>
       <c r="AR9">
-        <v>134</v>
+        <v>111.5</v>
       </c>
       <c r="AS9" s="18">
-        <v>8.933332999999999</v>
+        <v>7.433333</v>
       </c>
       <c r="AT9" s="18">
-        <v>8.933332999999999</v>
+        <v>7.433333</v>
       </c>
       <c r="AU9">
-        <v>40.06</v>
+        <v>43.39</v>
       </c>
     </row>
     <row r="10" spans="1:47">
@@ -9653,7 +9653,7 @@
         <v>0</v>
       </c>
       <c r="AU10">
-        <v>0.3</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="11" spans="1:47">
@@ -9775,19 +9775,19 @@
         <v>13</v>
       </c>
       <c r="AQ11">
-        <v>99</v>
+        <v>83.5</v>
       </c>
       <c r="AR11">
-        <v>99</v>
+        <v>83.5</v>
       </c>
       <c r="AS11" s="18">
-        <v>7.615385</v>
+        <v>6.423077</v>
       </c>
       <c r="AT11" s="18">
-        <v>7.615385</v>
+        <v>6.423077</v>
       </c>
       <c r="AU11">
-        <v>29.67</v>
+        <v>33.39</v>
       </c>
     </row>
     <row r="12" spans="1:47">
@@ -9909,16 +9909,16 @@
         <v>10</v>
       </c>
       <c r="AQ12">
+        <v>-10</v>
+      </c>
+      <c r="AR12">
+        <v>-10</v>
+      </c>
+      <c r="AS12" s="18">
         <v>-1</v>
       </c>
-      <c r="AR12">
+      <c r="AT12" s="18">
         <v>-1</v>
-      </c>
-      <c r="AS12" s="18">
-        <v>-0.1</v>
-      </c>
-      <c r="AT12" s="18">
-        <v>-0.1</v>
       </c>
       <c r="AU12">
         <v>0</v>
@@ -10043,19 +10043,19 @@
         <v>14</v>
       </c>
       <c r="AQ13">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="AR13">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="AS13" s="18">
-        <v>4.785714</v>
+        <v>3.357143</v>
       </c>
       <c r="AT13" s="18">
-        <v>4.785714</v>
+        <v>3.357143</v>
       </c>
       <c r="AU13">
-        <v>20.18</v>
+        <v>20.36</v>
       </c>
     </row>
     <row r="14" spans="1:47">
@@ -10183,7 +10183,7 @@
         <v>-1</v>
       </c>
       <c r="AU14">
-        <v>0</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="15" spans="1:47">
@@ -10305,19 +10305,19 @@
         <v>16</v>
       </c>
       <c r="AQ15">
-        <v>54</v>
+        <v>51.5</v>
       </c>
       <c r="AR15">
-        <v>54</v>
+        <v>51.5</v>
       </c>
       <c r="AS15" s="18">
-        <v>3.375</v>
+        <v>3.21875</v>
       </c>
       <c r="AT15" s="18">
-        <v>3.375</v>
+        <v>3.21875</v>
       </c>
       <c r="AU15">
-        <v>16.32</v>
+        <v>21.96</v>
       </c>
     </row>
     <row r="16" spans="1:47">
@@ -10439,19 +10439,19 @@
         <v>15</v>
       </c>
       <c r="AQ16">
-        <v>167</v>
+        <v>164.5</v>
       </c>
       <c r="AR16">
-        <v>167</v>
+        <v>164.5</v>
       </c>
       <c r="AS16" s="18">
-        <v>11.133333</v>
+        <v>10.966667</v>
       </c>
       <c r="AT16" s="18">
-        <v>11.133333</v>
+        <v>10.966667</v>
       </c>
       <c r="AU16">
-        <v>49.85</v>
+        <v>62.32</v>
       </c>
     </row>
     <row r="17" spans="1:47">
@@ -10573,19 +10573,19 @@
         <v>16</v>
       </c>
       <c r="AQ17">
-        <v>336</v>
+        <v>265.5</v>
       </c>
       <c r="AR17">
-        <v>336</v>
+        <v>265.5</v>
       </c>
       <c r="AS17" s="18">
-        <v>21</v>
+        <v>16.59375</v>
       </c>
       <c r="AT17" s="18">
-        <v>21</v>
+        <v>16.59375</v>
       </c>
       <c r="AU17">
-        <v>100</v>
+        <v>98.39</v>
       </c>
     </row>
     <row r="18" spans="1:47">
@@ -11680,28 +11680,28 @@
         <v>14</v>
       </c>
       <c r="K2">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="L2">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="M2" s="18">
-        <v>9.857143000000001</v>
+        <v>8.357143000000001</v>
       </c>
       <c r="N2" s="18">
-        <v>9.857143000000001</v>
+        <v>8.357143000000001</v>
       </c>
       <c r="O2" t="s">
         <v>410</v>
       </c>
       <c r="P2">
-        <v>41.25</v>
+        <v>45.36</v>
       </c>
       <c r="Q2">
         <v>5</v>
       </c>
       <c r="R2" s="18">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -11730,25 +11730,25 @@
         <v>16</v>
       </c>
       <c r="K3">
-        <v>33</v>
+        <v>5.5</v>
       </c>
       <c r="L3">
-        <v>33</v>
+        <v>5.5</v>
       </c>
       <c r="M3" s="18">
-        <v>2.0625</v>
+        <v>0.34375</v>
       </c>
       <c r="N3" s="18">
-        <v>2.0625</v>
+        <v>0.34375</v>
       </c>
       <c r="O3" t="s">
         <v>410</v>
       </c>
       <c r="P3">
-        <v>10.09</v>
+        <v>5.54</v>
       </c>
       <c r="Q3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R3" s="18">
         <v>13</v>
@@ -11783,28 +11783,28 @@
         <v>16</v>
       </c>
       <c r="K4">
-        <v>324</v>
+        <v>270</v>
       </c>
       <c r="L4">
-        <v>324</v>
+        <v>270</v>
       </c>
       <c r="M4" s="18">
-        <v>20.25</v>
+        <v>16.875</v>
       </c>
       <c r="N4" s="18">
-        <v>20.25</v>
+        <v>16.875</v>
       </c>
       <c r="O4" t="s">
         <v>410</v>
       </c>
       <c r="P4">
-        <v>96.44</v>
+        <v>100</v>
       </c>
       <c r="Q4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R4" s="18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -11833,28 +11833,28 @@
         <v>1</v>
       </c>
       <c r="K5">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="L5">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="M5" s="18">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="N5" s="18">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="O5" t="s">
         <v>410</v>
       </c>
       <c r="P5">
-        <v>2.97</v>
+        <v>6.96</v>
       </c>
       <c r="Q5">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R5" s="18">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -11886,22 +11886,22 @@
         <v>15</v>
       </c>
       <c r="K6">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="L6">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="M6" s="18">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="N6" s="18">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="O6" t="s">
         <v>410</v>
       </c>
       <c r="P6">
-        <v>59.05</v>
+        <v>73.20999999999999</v>
       </c>
       <c r="Q6">
         <v>3</v>
@@ -11936,28 +11936,28 @@
         <v>16</v>
       </c>
       <c r="K7">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="L7">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="M7" s="18">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="N7" s="18">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="O7" t="s">
         <v>410</v>
       </c>
       <c r="P7">
-        <v>20.47</v>
+        <v>23.57</v>
       </c>
       <c r="Q7">
         <v>9</v>
       </c>
       <c r="R7" s="18">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -11986,22 +11986,22 @@
         <v>15</v>
       </c>
       <c r="K8">
-        <v>135</v>
+        <v>116.5</v>
       </c>
       <c r="L8">
-        <v>135</v>
+        <v>116.5</v>
       </c>
       <c r="M8" s="18">
-        <v>9</v>
+        <v>7.766667</v>
       </c>
       <c r="N8" s="18">
-        <v>9</v>
+        <v>7.766667</v>
       </c>
       <c r="O8" t="s">
         <v>410</v>
       </c>
       <c r="P8">
-        <v>40.36</v>
+        <v>45.18</v>
       </c>
       <c r="Q8">
         <v>6</v>
@@ -12039,22 +12039,22 @@
         <v>15</v>
       </c>
       <c r="K9">
-        <v>134</v>
+        <v>111.5</v>
       </c>
       <c r="L9">
-        <v>134</v>
+        <v>111.5</v>
       </c>
       <c r="M9" s="18">
-        <v>8.933332999999999</v>
+        <v>7.433333</v>
       </c>
       <c r="N9" s="18">
-        <v>8.933332999999999</v>
+        <v>7.433333</v>
       </c>
       <c r="O9" t="s">
         <v>410</v>
       </c>
       <c r="P9">
-        <v>40.06</v>
+        <v>43.39</v>
       </c>
       <c r="Q9">
         <v>7</v>
@@ -12104,7 +12104,7 @@
         <v>410</v>
       </c>
       <c r="P10">
-        <v>0.3</v>
+        <v>3.57</v>
       </c>
       <c r="Q10">
         <v>14</v>
@@ -12139,22 +12139,22 @@
         <v>13</v>
       </c>
       <c r="K11">
-        <v>99</v>
+        <v>83.5</v>
       </c>
       <c r="L11">
-        <v>99</v>
+        <v>83.5</v>
       </c>
       <c r="M11" s="18">
-        <v>7.615385</v>
+        <v>6.423077</v>
       </c>
       <c r="N11" s="18">
-        <v>7.615385</v>
+        <v>6.423077</v>
       </c>
       <c r="O11" t="s">
         <v>410</v>
       </c>
       <c r="P11">
-        <v>29.67</v>
+        <v>33.39</v>
       </c>
       <c r="Q11">
         <v>8</v>
@@ -12189,16 +12189,16 @@
         <v>10</v>
       </c>
       <c r="K12">
+        <v>-10</v>
+      </c>
+      <c r="L12">
+        <v>-10</v>
+      </c>
+      <c r="M12" s="18">
         <v>-1</v>
       </c>
-      <c r="L12">
+      <c r="N12" s="18">
         <v>-1</v>
-      </c>
-      <c r="M12" s="18">
-        <v>-0.1</v>
-      </c>
-      <c r="N12" s="18">
-        <v>-0.1</v>
       </c>
       <c r="O12" t="s">
         <v>410</v>
@@ -12207,7 +12207,7 @@
         <v>0</v>
       </c>
       <c r="Q12">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R12" s="18">
         <v>15</v>
@@ -12239,28 +12239,28 @@
         <v>14</v>
       </c>
       <c r="K13">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="L13">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="M13" s="18">
-        <v>4.785714</v>
+        <v>3.357143</v>
       </c>
       <c r="N13" s="18">
-        <v>4.785714</v>
+        <v>3.357143</v>
       </c>
       <c r="O13" t="s">
         <v>410</v>
       </c>
       <c r="P13">
-        <v>20.18</v>
+        <v>20.36</v>
       </c>
       <c r="Q13">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R13" s="18">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -12304,10 +12304,10 @@
         <v>410</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Q14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R14" s="18">
         <v>16</v>
@@ -12339,25 +12339,25 @@
         <v>16</v>
       </c>
       <c r="K15">
-        <v>54</v>
+        <v>51.5</v>
       </c>
       <c r="L15">
-        <v>54</v>
+        <v>51.5</v>
       </c>
       <c r="M15" s="18">
-        <v>3.375</v>
+        <v>3.21875</v>
       </c>
       <c r="N15" s="18">
-        <v>3.375</v>
+        <v>3.21875</v>
       </c>
       <c r="O15" t="s">
         <v>410</v>
       </c>
       <c r="P15">
-        <v>16.32</v>
+        <v>21.96</v>
       </c>
       <c r="Q15">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R15" s="18">
         <v>12</v>
@@ -12389,22 +12389,22 @@
         <v>15</v>
       </c>
       <c r="K16">
-        <v>167</v>
+        <v>164.5</v>
       </c>
       <c r="L16">
-        <v>167</v>
+        <v>164.5</v>
       </c>
       <c r="M16" s="18">
-        <v>11.133333</v>
+        <v>10.966667</v>
       </c>
       <c r="N16" s="18">
-        <v>11.133333</v>
+        <v>10.966667</v>
       </c>
       <c r="O16" t="s">
         <v>410</v>
       </c>
       <c r="P16">
-        <v>49.85</v>
+        <v>62.32</v>
       </c>
       <c r="Q16">
         <v>4</v>
@@ -12439,28 +12439,28 @@
         <v>16</v>
       </c>
       <c r="K17">
-        <v>336</v>
+        <v>265.5</v>
       </c>
       <c r="L17">
-        <v>336</v>
+        <v>265.5</v>
       </c>
       <c r="M17" s="18">
-        <v>21</v>
+        <v>16.59375</v>
       </c>
       <c r="N17" s="18">
-        <v>21</v>
+        <v>16.59375</v>
       </c>
       <c r="O17" t="s">
         <v>410</v>
       </c>
       <c r="P17">
-        <v>100</v>
+        <v>98.39</v>
       </c>
       <c r="Q17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R17" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:18">
@@ -13924,13 +13924,13 @@
         <v>1</v>
       </c>
       <c r="B92" s="12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C92" s="12">
-        <v>336</v>
+        <v>270</v>
       </c>
       <c r="D92" s="12">
-        <v>21</v>
+        <v>16.875</v>
       </c>
       <c r="E92" s="12">
         <v>16</v>
@@ -13941,13 +13941,13 @@
         <v>2</v>
       </c>
       <c r="B93" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C93" s="12">
-        <v>324</v>
+        <v>265.5</v>
       </c>
       <c r="D93" s="12">
-        <v>20.25</v>
+        <v>16.59375</v>
       </c>
       <c r="E93" s="12">
         <v>16</v>
@@ -13961,10 +13961,10 @@
         <v>61</v>
       </c>
       <c r="C94" s="12">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D94" s="12">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="E94" s="12">
         <v>15</v>
@@ -13978,10 +13978,10 @@
         <v>62</v>
       </c>
       <c r="C95" s="12">
-        <v>167</v>
+        <v>164.5</v>
       </c>
       <c r="D95" s="12">
-        <v>11.133333</v>
+        <v>10.966667</v>
       </c>
       <c r="E95" s="12">
         <v>15</v>
@@ -13995,10 +13995,10 @@
         <v>63</v>
       </c>
       <c r="C96" s="12">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="D96" s="12">
-        <v>9.857143000000001</v>
+        <v>8.357143000000001</v>
       </c>
       <c r="E96" s="12">
         <v>14</v>
@@ -14012,10 +14012,10 @@
         <v>65</v>
       </c>
       <c r="C97" s="12">
-        <v>135</v>
+        <v>116.5</v>
       </c>
       <c r="D97" s="12">
-        <v>9</v>
+        <v>7.766667</v>
       </c>
       <c r="E97" s="12">
         <v>15</v>
@@ -14029,10 +14029,10 @@
         <v>64</v>
       </c>
       <c r="C98" s="12">
-        <v>134</v>
+        <v>111.5</v>
       </c>
       <c r="D98" s="12">
-        <v>8.933332999999999</v>
+        <v>7.433333</v>
       </c>
       <c r="E98" s="12">
         <v>15</v>
@@ -14046,10 +14046,10 @@
         <v>71</v>
       </c>
       <c r="C99" s="12">
-        <v>99</v>
+        <v>83.5</v>
       </c>
       <c r="D99" s="12">
-        <v>7.615385</v>
+        <v>6.423077</v>
       </c>
       <c r="E99" s="12">
         <v>13</v>
@@ -14063,10 +14063,10 @@
         <v>68</v>
       </c>
       <c r="C100" s="12">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="D100" s="12">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="E100" s="12">
         <v>16</v>
@@ -14077,16 +14077,16 @@
         <v>10</v>
       </c>
       <c r="B101" s="12" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C101" s="12">
-        <v>67</v>
+        <v>51.5</v>
       </c>
       <c r="D101" s="12">
-        <v>4.785714</v>
+        <v>3.21875</v>
       </c>
       <c r="E101" s="12">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -14094,16 +14094,16 @@
         <v>11</v>
       </c>
       <c r="B102" s="12" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C102" s="12">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D102" s="12">
-        <v>3.375</v>
+        <v>3.357143</v>
       </c>
       <c r="E102" s="12">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -14111,16 +14111,16 @@
         <v>12</v>
       </c>
       <c r="B103" s="12" t="s">
-        <v>69</v>
+        <v>127</v>
       </c>
       <c r="C103" s="12">
-        <v>33</v>
+        <v>9.5</v>
       </c>
       <c r="D103" s="12">
-        <v>2.0625</v>
+        <v>9.5</v>
       </c>
       <c r="E103" s="12">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -14128,16 +14128,16 @@
         <v>13</v>
       </c>
       <c r="B104" s="12" t="s">
-        <v>127</v>
+        <v>69</v>
       </c>
       <c r="C104" s="12">
-        <v>9</v>
+        <v>5.5</v>
       </c>
       <c r="D104" s="12">
-        <v>9</v>
+        <v>0.34375</v>
       </c>
       <c r="E104" s="12">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -14162,16 +14162,16 @@
         <v>15</v>
       </c>
       <c r="B106" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C106" s="12">
         <v>-1</v>
       </c>
       <c r="D106" s="12">
-        <v>-0.1</v>
+        <v>-1</v>
       </c>
       <c r="E106" s="12">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -14179,16 +14179,16 @@
         <v>16</v>
       </c>
       <c r="B107" s="12" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C107" s="12">
-        <v>-1</v>
+        <v>-10</v>
       </c>
       <c r="D107" s="12">
         <v>-1</v>
       </c>
       <c r="E107" s="12">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -14854,10 +14854,10 @@
         <v>40</v>
       </c>
       <c r="L3" s="12">
-        <v>355</v>
+        <v>297.5</v>
       </c>
       <c r="M3" s="12">
-        <v>5.071429</v>
+        <v>4.25</v>
       </c>
       <c r="N3" s="12">
         <v>9</v>
@@ -14904,10 +14904,10 @@
         <v>21</v>
       </c>
       <c r="L4" s="12">
-        <v>166</v>
+        <v>116</v>
       </c>
       <c r="M4" s="12">
-        <v>5.1875</v>
+        <v>3.625</v>
       </c>
       <c r="N4" s="12">
         <v>10</v>
@@ -14954,10 +14954,10 @@
         <v>45</v>
       </c>
       <c r="L5" s="12">
-        <v>865</v>
+        <v>699.5</v>
       </c>
       <c r="M5" s="12">
-        <v>14.180328</v>
+        <v>11.467213</v>
       </c>
       <c r="N5" s="12">
         <v>19</v>
@@ -15004,10 +15004,10 @@
         <v>14</v>
       </c>
       <c r="L6" s="12">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="M6" s="12">
-        <v>12.064516</v>
+        <v>11.903226</v>
       </c>
       <c r="N6" s="12">
         <v>8</v>
@@ -15146,10 +15146,10 @@
         <v>105</v>
       </c>
       <c r="L11" s="12">
-        <v>1580.1</v>
+        <v>1320.6</v>
       </c>
       <c r="M11" s="12">
-        <v>8.061735000000001</v>
+        <v>6.737755</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -15187,10 +15187,10 @@
         <v>17</v>
       </c>
       <c r="L12" s="12">
-        <v>129</v>
+        <v>110.5</v>
       </c>
       <c r="M12" s="12">
-        <v>4.16129</v>
+        <v>3.564516</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -15274,10 +15274,10 @@
         <v>52</v>
       </c>
       <c r="L16" s="12">
-        <v>794</v>
+        <v>693.5</v>
       </c>
       <c r="M16" s="12">
-        <v>13.233333</v>
+        <v>11.558333</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -15315,10 +15315,10 @@
         <v>70</v>
       </c>
       <c r="L17" s="12">
-        <v>915.1</v>
+        <v>737.6</v>
       </c>
       <c r="M17" s="12">
-        <v>5.479641</v>
+        <v>4.416766</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -15393,10 +15393,10 @@
         <v>0.375</v>
       </c>
       <c r="J21" s="12">
-        <v>135</v>
+        <v>116.5</v>
       </c>
       <c r="K21" s="12">
-        <v>9</v>
+        <v>7.766667</v>
       </c>
       <c r="L21" s="12">
         <v>15</v>
@@ -15431,10 +15431,10 @@
         <v>0.384615</v>
       </c>
       <c r="J22" s="12">
-        <v>99</v>
+        <v>83.5</v>
       </c>
       <c r="K22" s="12">
-        <v>7.615385</v>
+        <v>6.423077</v>
       </c>
       <c r="L22" s="12">
         <v>13</v>
@@ -15469,10 +15469,10 @@
         <v>0.2</v>
       </c>
       <c r="J23" s="12">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="K23" s="12">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="L23" s="12">
         <v>16</v>
@@ -15507,10 +15507,10 @@
         <v>0.07142900000000001</v>
       </c>
       <c r="J24" s="12">
-        <v>54</v>
+        <v>51.5</v>
       </c>
       <c r="K24" s="12">
-        <v>3.375</v>
+        <v>3.21875</v>
       </c>
       <c r="L24" s="12">
         <v>16</v>
@@ -15545,10 +15545,10 @@
         <v>0</v>
       </c>
       <c r="J25" s="12">
+        <v>-10</v>
+      </c>
+      <c r="K25" s="12">
         <v>-1</v>
-      </c>
-      <c r="K25" s="12">
-        <v>-0.1</v>
       </c>
       <c r="L25" s="12">
         <v>10</v>
@@ -15626,10 +15626,10 @@
         <v>0.347826</v>
       </c>
       <c r="J29" s="12">
-        <v>134</v>
+        <v>111.5</v>
       </c>
       <c r="K29" s="12">
-        <v>8.933332999999999</v>
+        <v>7.433333</v>
       </c>
       <c r="L29" s="12">
         <v>15</v>
@@ -15664,10 +15664,10 @@
         <v>0.15</v>
       </c>
       <c r="J30" s="12">
-        <v>33</v>
+        <v>5.5</v>
       </c>
       <c r="K30" s="12">
-        <v>2.0625</v>
+        <v>0.34375</v>
       </c>
       <c r="L30" s="12">
         <v>16</v>
@@ -15757,34 +15757,34 @@
         <v>1</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C35" s="12" t="s">
         <v>85</v>
       </c>
       <c r="D35" s="12">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="E35" s="12">
-        <v>3.5625</v>
+        <v>2.25</v>
       </c>
       <c r="F35" s="12">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="G35" s="12">
-        <v>0.375</v>
+        <v>1.1875</v>
       </c>
       <c r="H35" s="12">
-        <v>0.500387</v>
+        <v>0.401337</v>
       </c>
       <c r="I35" s="12">
-        <v>0.483051</v>
+        <v>0.423529</v>
       </c>
       <c r="J35" s="12">
-        <v>336</v>
+        <v>270</v>
       </c>
       <c r="K35" s="12">
-        <v>21</v>
+        <v>16.875</v>
       </c>
       <c r="L35" s="12">
         <v>16</v>
@@ -15795,34 +15795,34 @@
         <v>2</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C36" s="12" t="s">
         <v>85</v>
       </c>
       <c r="D36" s="12">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="E36" s="12">
-        <v>2.25</v>
+        <v>3.5625</v>
       </c>
       <c r="F36" s="12">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="G36" s="12">
-        <v>1.1875</v>
+        <v>0.375</v>
       </c>
       <c r="H36" s="12">
-        <v>0.401337</v>
+        <v>0.500387</v>
       </c>
       <c r="I36" s="12">
-        <v>0.423529</v>
+        <v>0.483051</v>
       </c>
       <c r="J36" s="12">
-        <v>324</v>
+        <v>265.5</v>
       </c>
       <c r="K36" s="12">
-        <v>20.25</v>
+        <v>16.59375</v>
       </c>
       <c r="L36" s="12">
         <v>16</v>
@@ -15857,10 +15857,10 @@
         <v>0.484848</v>
       </c>
       <c r="J37" s="12">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="K37" s="12">
-        <v>9.857143000000001</v>
+        <v>8.357143000000001</v>
       </c>
       <c r="L37" s="12">
         <v>14</v>
@@ -15895,10 +15895,10 @@
         <v>0.407407</v>
       </c>
       <c r="J38" s="12">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="K38" s="12">
-        <v>4.785714</v>
+        <v>3.357143</v>
       </c>
       <c r="L38" s="12">
         <v>14</v>
@@ -16012,10 +16012,10 @@
         <v>0.431373</v>
       </c>
       <c r="J43" s="12">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="K43" s="12">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="L43" s="12">
         <v>15</v>
@@ -16050,10 +16050,10 @@
         <v>0.575758</v>
       </c>
       <c r="J44" s="12">
-        <v>167</v>
+        <v>164.5</v>
       </c>
       <c r="K44" s="12">
-        <v>11.133333</v>
+        <v>10.966667</v>
       </c>
       <c r="L44" s="12">
         <v>15</v>
@@ -16088,10 +16088,10 @@
         <v>0.333333</v>
       </c>
       <c r="J45" s="12">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="K45" s="12">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="L45" s="12">
         <v>1</v>
@@ -16266,34 +16266,34 @@
         <v>1</v>
       </c>
       <c r="B55" s="12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C55" s="12" t="s">
         <v>85</v>
       </c>
       <c r="D55" s="12">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="E55" s="12">
-        <v>3.5625</v>
+        <v>2.25</v>
       </c>
       <c r="F55" s="12">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="G55" s="12">
-        <v>0.375</v>
+        <v>1.1875</v>
       </c>
       <c r="H55" s="12">
-        <v>0.500387</v>
+        <v>0.401337</v>
       </c>
       <c r="I55" s="12">
-        <v>0.483051</v>
+        <v>0.423529</v>
       </c>
       <c r="J55" s="12">
-        <v>336</v>
+        <v>270</v>
       </c>
       <c r="K55" s="12">
-        <v>21</v>
+        <v>16.875</v>
       </c>
       <c r="L55" s="12">
         <v>16</v>
@@ -16304,34 +16304,34 @@
         <v>2</v>
       </c>
       <c r="B56" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C56" s="12" t="s">
         <v>85</v>
       </c>
       <c r="D56" s="12">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="E56" s="12">
-        <v>2.25</v>
+        <v>3.5625</v>
       </c>
       <c r="F56" s="12">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="G56" s="12">
-        <v>1.1875</v>
+        <v>0.375</v>
       </c>
       <c r="H56" s="12">
-        <v>0.401337</v>
+        <v>0.500387</v>
       </c>
       <c r="I56" s="12">
-        <v>0.423529</v>
+        <v>0.483051</v>
       </c>
       <c r="J56" s="12">
-        <v>324</v>
+        <v>265.5</v>
       </c>
       <c r="K56" s="12">
-        <v>20.25</v>
+        <v>16.59375</v>
       </c>
       <c r="L56" s="12">
         <v>16</v>
@@ -16366,10 +16366,10 @@
         <v>0.431373</v>
       </c>
       <c r="J57" s="12">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="K57" s="12">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="L57" s="12">
         <v>15</v>
@@ -16404,10 +16404,10 @@
         <v>0.575758</v>
       </c>
       <c r="J58" s="12">
-        <v>167</v>
+        <v>164.5</v>
       </c>
       <c r="K58" s="12">
-        <v>11.133333</v>
+        <v>10.966667</v>
       </c>
       <c r="L58" s="12">
         <v>15</v>
@@ -16442,10 +16442,10 @@
         <v>0.484848</v>
       </c>
       <c r="J59" s="12">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="K59" s="12">
-        <v>9.857143000000001</v>
+        <v>8.357143000000001</v>
       </c>
       <c r="L59" s="12">
         <v>14</v>
@@ -16480,10 +16480,10 @@
         <v>0.347826</v>
       </c>
       <c r="J60" s="12">
-        <v>134</v>
+        <v>111.5</v>
       </c>
       <c r="K60" s="12">
-        <v>8.933332999999999</v>
+        <v>7.433333</v>
       </c>
       <c r="L60" s="12">
         <v>15</v>
@@ -16518,10 +16518,10 @@
         <v>0.384615</v>
       </c>
       <c r="J61" s="12">
-        <v>99</v>
+        <v>83.5</v>
       </c>
       <c r="K61" s="12">
-        <v>7.615385</v>
+        <v>6.423077</v>
       </c>
       <c r="L61" s="12">
         <v>13</v>
@@ -16556,10 +16556,10 @@
         <v>0.2</v>
       </c>
       <c r="J62" s="12">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="K62" s="12">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="L62" s="12">
         <v>16</v>
@@ -16570,37 +16570,37 @@
         <v>9</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C63" s="12" t="s">
         <v>85</v>
       </c>
       <c r="D63" s="12">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E63" s="12">
-        <v>0.785714</v>
+        <v>0.0625</v>
       </c>
       <c r="F63" s="12">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G63" s="12">
-        <v>0.285714</v>
+        <v>0.875</v>
       </c>
       <c r="H63" s="12">
-        <v>0.358974</v>
+        <v>0.033333</v>
       </c>
       <c r="I63" s="12">
-        <v>0.407407</v>
+        <v>0.07142900000000001</v>
       </c>
       <c r="J63" s="12">
-        <v>67</v>
+        <v>51.5</v>
       </c>
       <c r="K63" s="12">
-        <v>4.785714</v>
+        <v>3.21875</v>
       </c>
       <c r="L63" s="12">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="64" spans="1:12">
@@ -16608,37 +16608,37 @@
         <v>10</v>
       </c>
       <c r="B64" s="12" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C64" s="12" t="s">
         <v>85</v>
       </c>
       <c r="D64" s="12">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E64" s="12">
-        <v>0.0625</v>
+        <v>0.785714</v>
       </c>
       <c r="F64" s="12">
+        <v>4</v>
+      </c>
+      <c r="G64" s="12">
+        <v>0.285714</v>
+      </c>
+      <c r="H64" s="12">
+        <v>0.358974</v>
+      </c>
+      <c r="I64" s="12">
+        <v>0.407407</v>
+      </c>
+      <c r="J64" s="12">
+        <v>47</v>
+      </c>
+      <c r="K64" s="12">
+        <v>3.357143</v>
+      </c>
+      <c r="L64" s="12">
         <v>14</v>
-      </c>
-      <c r="G64" s="12">
-        <v>0.875</v>
-      </c>
-      <c r="H64" s="12">
-        <v>0.033333</v>
-      </c>
-      <c r="I64" s="12">
-        <v>0.07142900000000001</v>
-      </c>
-      <c r="J64" s="12">
-        <v>54</v>
-      </c>
-      <c r="K64" s="12">
-        <v>3.375</v>
-      </c>
-      <c r="L64" s="12">
-        <v>16</v>
       </c>
     </row>
     <row r="65" spans="1:12">
@@ -16646,37 +16646,37 @@
         <v>11</v>
       </c>
       <c r="B65" s="12" t="s">
-        <v>69</v>
+        <v>127</v>
       </c>
       <c r="C65" s="12" t="s">
         <v>85</v>
       </c>
       <c r="D65" s="12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E65" s="12">
-        <v>0.1875</v>
+        <v>1</v>
       </c>
       <c r="F65" s="12">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G65" s="12">
-        <v>0.875</v>
+        <v>0</v>
       </c>
       <c r="H65" s="12">
-        <v>0.133333</v>
+        <v>0.333333</v>
       </c>
       <c r="I65" s="12">
-        <v>0.15</v>
+        <v>0.333333</v>
       </c>
       <c r="J65" s="12">
-        <v>33</v>
+        <v>9.5</v>
       </c>
       <c r="K65" s="12">
-        <v>2.0625</v>
+        <v>9.5</v>
       </c>
       <c r="L65" s="12">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:12">
@@ -16684,37 +16684,37 @@
         <v>12</v>
       </c>
       <c r="B66" s="12" t="s">
-        <v>127</v>
+        <v>69</v>
       </c>
       <c r="C66" s="12" t="s">
         <v>85</v>
       </c>
       <c r="D66" s="12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E66" s="12">
-        <v>1</v>
+        <v>0.1875</v>
       </c>
       <c r="F66" s="12">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G66" s="12">
-        <v>0</v>
+        <v>0.875</v>
       </c>
       <c r="H66" s="12">
-        <v>0.333333</v>
+        <v>0.133333</v>
       </c>
       <c r="I66" s="12">
-        <v>0.333333</v>
+        <v>0.15</v>
       </c>
       <c r="J66" s="12">
-        <v>9</v>
+        <v>5.5</v>
       </c>
       <c r="K66" s="12">
-        <v>9</v>
+        <v>0.34375</v>
       </c>
       <c r="L66" s="12">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="67" spans="1:12">
@@ -16758,7 +16758,7 @@
         <v>14</v>
       </c>
       <c r="B68" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C68" s="12" t="s">
         <v>85</v>
@@ -16773,22 +16773,20 @@
         <v>1</v>
       </c>
       <c r="G68" s="12">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="H68" s="12">
         <v>0</v>
       </c>
-      <c r="I68" s="12">
-        <v>0</v>
-      </c>
+      <c r="I68" s="12"/>
       <c r="J68" s="12">
         <v>-1</v>
       </c>
       <c r="K68" s="12">
-        <v>-0.1</v>
+        <v>-1</v>
       </c>
       <c r="L68" s="12">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:12">
@@ -16796,7 +16794,7 @@
         <v>15</v>
       </c>
       <c r="B69" s="12" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C69" s="12" t="s">
         <v>85</v>
@@ -16811,20 +16809,22 @@
         <v>1</v>
       </c>
       <c r="G69" s="12">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="H69" s="12">
         <v>0</v>
       </c>
-      <c r="I69" s="12"/>
+      <c r="I69" s="12">
+        <v>0</v>
+      </c>
       <c r="J69" s="12">
-        <v>-1</v>
+        <v>-10</v>
       </c>
       <c r="K69" s="12">
         <v>-1</v>
       </c>
       <c r="L69" s="12">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="71" spans="1:12">
@@ -16899,10 +16899,10 @@
         <v>0.375</v>
       </c>
       <c r="J73" s="12">
-        <v>135</v>
+        <v>116.5</v>
       </c>
       <c r="K73" s="12">
-        <v>9</v>
+        <v>7.766667</v>
       </c>
       <c r="L73" s="12">
         <v>15</v>
@@ -16980,10 +16980,10 @@
         <v>0.423529</v>
       </c>
       <c r="J77" s="12">
-        <v>324</v>
+        <v>270</v>
       </c>
       <c r="K77" s="12">
-        <v>20.25</v>
+        <v>16.875</v>
       </c>
       <c r="L77" s="12">
         <v>16</v>
@@ -17018,10 +17018,10 @@
         <v>0.431373</v>
       </c>
       <c r="J78" s="12">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="K78" s="12">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="L78" s="12">
         <v>15</v>
@@ -17056,10 +17056,10 @@
         <v>0.484848</v>
       </c>
       <c r="J79" s="12">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="K79" s="12">
-        <v>9.857143000000001</v>
+        <v>8.357143000000001</v>
       </c>
       <c r="L79" s="12">
         <v>14</v>
@@ -17094,10 +17094,10 @@
         <v>0.347826</v>
       </c>
       <c r="J80" s="12">
-        <v>134</v>
+        <v>111.5</v>
       </c>
       <c r="K80" s="12">
-        <v>8.933332999999999</v>
+        <v>7.433333</v>
       </c>
       <c r="L80" s="12">
         <v>15</v>
@@ -17175,10 +17175,10 @@
         <v>0.483051</v>
       </c>
       <c r="J84" s="12">
-        <v>336</v>
+        <v>265.5</v>
       </c>
       <c r="K84" s="12">
-        <v>21</v>
+        <v>16.59375</v>
       </c>
       <c r="L84" s="12">
         <v>16</v>
@@ -17213,10 +17213,10 @@
         <v>0.575758</v>
       </c>
       <c r="J85" s="12">
-        <v>167</v>
+        <v>164.5</v>
       </c>
       <c r="K85" s="12">
-        <v>11.133333</v>
+        <v>10.966667</v>
       </c>
       <c r="L85" s="12">
         <v>15</v>
@@ -17251,10 +17251,10 @@
         <v>0.375</v>
       </c>
       <c r="J86" s="12">
-        <v>135</v>
+        <v>116.5</v>
       </c>
       <c r="K86" s="12">
-        <v>9</v>
+        <v>7.766667</v>
       </c>
       <c r="L86" s="12">
         <v>15</v>
@@ -17289,10 +17289,10 @@
         <v>0.384615</v>
       </c>
       <c r="J87" s="12">
-        <v>99</v>
+        <v>83.5</v>
       </c>
       <c r="K87" s="12">
-        <v>7.615385</v>
+        <v>6.423077</v>
       </c>
       <c r="L87" s="12">
         <v>13</v>
@@ -17327,10 +17327,10 @@
         <v>0.2</v>
       </c>
       <c r="J88" s="12">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="K88" s="12">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="L88" s="12">
         <v>16</v>
@@ -17341,37 +17341,37 @@
         <v>6</v>
       </c>
       <c r="B89" s="12" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C89" s="12" t="s">
         <v>85</v>
       </c>
       <c r="D89" s="12">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E89" s="12">
-        <v>0.785714</v>
+        <v>0.0625</v>
       </c>
       <c r="F89" s="12">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G89" s="12">
-        <v>0.285714</v>
+        <v>0.875</v>
       </c>
       <c r="H89" s="12">
-        <v>0.358974</v>
+        <v>0.033333</v>
       </c>
       <c r="I89" s="12">
-        <v>0.407407</v>
+        <v>0.07142900000000001</v>
       </c>
       <c r="J89" s="12">
-        <v>67</v>
+        <v>51.5</v>
       </c>
       <c r="K89" s="12">
-        <v>4.785714</v>
+        <v>3.21875</v>
       </c>
       <c r="L89" s="12">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="90" spans="1:12">
@@ -17379,37 +17379,37 @@
         <v>7</v>
       </c>
       <c r="B90" s="12" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C90" s="12" t="s">
         <v>85</v>
       </c>
       <c r="D90" s="12">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E90" s="12">
-        <v>0.0625</v>
+        <v>0.785714</v>
       </c>
       <c r="F90" s="12">
+        <v>4</v>
+      </c>
+      <c r="G90" s="12">
+        <v>0.285714</v>
+      </c>
+      <c r="H90" s="12">
+        <v>0.358974</v>
+      </c>
+      <c r="I90" s="12">
+        <v>0.407407</v>
+      </c>
+      <c r="J90" s="12">
+        <v>47</v>
+      </c>
+      <c r="K90" s="12">
+        <v>3.357143</v>
+      </c>
+      <c r="L90" s="12">
         <v>14</v>
-      </c>
-      <c r="G90" s="12">
-        <v>0.875</v>
-      </c>
-      <c r="H90" s="12">
-        <v>0.033333</v>
-      </c>
-      <c r="I90" s="12">
-        <v>0.07142900000000001</v>
-      </c>
-      <c r="J90" s="12">
-        <v>54</v>
-      </c>
-      <c r="K90" s="12">
-        <v>3.375</v>
-      </c>
-      <c r="L90" s="12">
-        <v>16</v>
       </c>
     </row>
     <row r="91" spans="1:12">
@@ -17417,37 +17417,37 @@
         <v>8</v>
       </c>
       <c r="B91" s="12" t="s">
-        <v>69</v>
+        <v>127</v>
       </c>
       <c r="C91" s="12" t="s">
         <v>85</v>
       </c>
       <c r="D91" s="12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E91" s="12">
-        <v>0.1875</v>
+        <v>1</v>
       </c>
       <c r="F91" s="12">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G91" s="12">
-        <v>0.875</v>
+        <v>0</v>
       </c>
       <c r="H91" s="12">
-        <v>0.133333</v>
+        <v>0.333333</v>
       </c>
       <c r="I91" s="12">
-        <v>0.15</v>
+        <v>0.333333</v>
       </c>
       <c r="J91" s="12">
-        <v>33</v>
+        <v>9.5</v>
       </c>
       <c r="K91" s="12">
-        <v>2.0625</v>
+        <v>9.5</v>
       </c>
       <c r="L91" s="12">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:12">
@@ -17455,37 +17455,37 @@
         <v>9</v>
       </c>
       <c r="B92" s="12" t="s">
-        <v>127</v>
+        <v>69</v>
       </c>
       <c r="C92" s="12" t="s">
         <v>85</v>
       </c>
       <c r="D92" s="12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E92" s="12">
-        <v>1</v>
+        <v>0.1875</v>
       </c>
       <c r="F92" s="12">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G92" s="12">
-        <v>0</v>
+        <v>0.875</v>
       </c>
       <c r="H92" s="12">
-        <v>0.333333</v>
+        <v>0.133333</v>
       </c>
       <c r="I92" s="12">
-        <v>0.333333</v>
+        <v>0.15</v>
       </c>
       <c r="J92" s="12">
-        <v>9</v>
+        <v>5.5</v>
       </c>
       <c r="K92" s="12">
-        <v>9</v>
+        <v>0.34375</v>
       </c>
       <c r="L92" s="12">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="93" spans="1:12">
@@ -17529,7 +17529,7 @@
         <v>11</v>
       </c>
       <c r="B94" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C94" s="12" t="s">
         <v>85</v>
@@ -17544,22 +17544,20 @@
         <v>1</v>
       </c>
       <c r="G94" s="12">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="H94" s="12">
         <v>0</v>
       </c>
-      <c r="I94" s="12">
-        <v>0</v>
-      </c>
+      <c r="I94" s="12"/>
       <c r="J94" s="12">
         <v>-1</v>
       </c>
       <c r="K94" s="12">
-        <v>-0.1</v>
+        <v>-1</v>
       </c>
       <c r="L94" s="12">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:12">
@@ -17567,7 +17565,7 @@
         <v>12</v>
       </c>
       <c r="B95" s="12" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C95" s="12" t="s">
         <v>85</v>
@@ -17582,20 +17580,22 @@
         <v>1</v>
       </c>
       <c r="G95" s="12">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="H95" s="12">
         <v>0</v>
       </c>
-      <c r="I95" s="12"/>
+      <c r="I95" s="12">
+        <v>0</v>
+      </c>
       <c r="J95" s="12">
-        <v>-1</v>
+        <v>-10</v>
       </c>
       <c r="K95" s="12">
         <v>-1</v>
       </c>
       <c r="L95" s="12">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -38064,19 +38064,19 @@
         <v>175</v>
       </c>
       <c r="L2">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="M2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N2">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="O2" s="19">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="Q2" t="s">
         <v>410</v>
@@ -38114,19 +38114,19 @@
         <v>89</v>
       </c>
       <c r="L3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M3">
+        <v>6</v>
+      </c>
+      <c r="N3">
+        <v>2</v>
+      </c>
+      <c r="O3" s="19">
+        <v>0</v>
+      </c>
+      <c r="P3">
         <v>4</v>
-      </c>
-      <c r="N3">
-        <v>2</v>
-      </c>
-      <c r="O3" s="19">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>2</v>
       </c>
       <c r="Q3" t="s">
         <v>410</v>
@@ -38167,19 +38167,19 @@
         <v>176</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="M4">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="N4">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="O4" s="19">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="Q4" t="s">
         <v>410</v>
@@ -38270,10 +38270,10 @@
         <v>89</v>
       </c>
       <c r="L6">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="M6">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="N6">
         <v>2</v>
@@ -38282,7 +38282,7 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="Q6" t="s">
         <v>410</v>
@@ -38320,19 +38320,19 @@
         <v>89</v>
       </c>
       <c r="L7">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="M7">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="N7">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="O7" s="19">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="Q7" t="s">
         <v>410</v>
@@ -38373,19 +38373,19 @@
         <v>178</v>
       </c>
       <c r="L8">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="M8">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N8">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="O8" s="19">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="Q8" t="s">
         <v>410</v>
@@ -38473,19 +38473,19 @@
         <v>89</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>-1.5</v>
       </c>
       <c r="M10">
         <v>5</v>
       </c>
       <c r="N10">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="O10" s="19">
         <v>0</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>-1.5</v>
       </c>
       <c r="Q10" t="s">
         <v>410</v>
@@ -38523,10 +38523,10 @@
         <v>89</v>
       </c>
       <c r="L11">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M11">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -38535,7 +38535,7 @@
         <v>0</v>
       </c>
       <c r="P11">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Q11" t="s">
         <v>410</v>
@@ -38573,19 +38573,19 @@
         <v>89</v>
       </c>
       <c r="L12">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="M12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N12">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="O12" s="19">
         <v>0</v>
       </c>
       <c r="P12">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="Q12" t="s">
         <v>410</v>
@@ -38623,10 +38623,10 @@
         <v>89</v>
       </c>
       <c r="L13">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="M13">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="N13">
         <v>2</v>
@@ -38635,7 +38635,7 @@
         <v>0</v>
       </c>
       <c r="P13">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="Q13" t="s">
         <v>410</v>
@@ -38673,19 +38673,19 @@
         <v>89</v>
       </c>
       <c r="L14">
-        <v>26</v>
+        <v>20.5</v>
       </c>
       <c r="M14">
-        <v>34</v>
+        <v>29.5</v>
       </c>
       <c r="N14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O14" s="19">
         <v>0</v>
       </c>
       <c r="P14">
-        <v>26</v>
+        <v>20.5</v>
       </c>
       <c r="Q14" t="s">
         <v>410</v>
@@ -38826,10 +38826,10 @@
         <v>175</v>
       </c>
       <c r="L17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M17">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="N17">
         <v>6</v>
@@ -38838,7 +38838,7 @@
         <v>6</v>
       </c>
       <c r="P17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q17" t="s">
         <v>410</v>
@@ -38876,19 +38876,19 @@
         <v>89</v>
       </c>
       <c r="L18">
-        <v>1</v>
+        <v>-4.5</v>
       </c>
       <c r="M18">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="N18">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O18" s="19">
         <v>0</v>
       </c>
       <c r="P18">
-        <v>1</v>
+        <v>-4.5</v>
       </c>
       <c r="Q18" t="s">
         <v>410</v>
@@ -38929,19 +38929,19 @@
         <v>176</v>
       </c>
       <c r="L19">
-        <v>37</v>
+        <v>32.5</v>
       </c>
       <c r="M19">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="N19">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="O19" s="19">
         <v>4</v>
       </c>
       <c r="P19">
-        <v>37</v>
+        <v>32.5</v>
       </c>
       <c r="Q19" t="s">
         <v>410</v>
@@ -38982,19 +38982,19 @@
         <v>177</v>
       </c>
       <c r="L20">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M20">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="N20">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O20" s="19">
         <v>2</v>
       </c>
       <c r="P20">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Q20" t="s">
         <v>410</v>
@@ -39032,19 +39032,19 @@
         <v>89</v>
       </c>
       <c r="L21">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M21">
         <v>18</v>
       </c>
       <c r="N21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O21" s="19">
         <v>2</v>
       </c>
       <c r="P21">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q21" t="s">
         <v>410</v>
@@ -39082,19 +39082,19 @@
         <v>89</v>
       </c>
       <c r="L22">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="M22">
-        <v>25</v>
+        <v>23.5</v>
       </c>
       <c r="N22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O22" s="19">
         <v>0</v>
       </c>
       <c r="P22">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="Q22" t="s">
         <v>410</v>
@@ -39135,19 +39135,19 @@
         <v>178</v>
       </c>
       <c r="L23">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="M23">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="N23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O23" s="19">
         <v>0</v>
       </c>
       <c r="P23">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="Q23" t="s">
         <v>410</v>
@@ -39185,19 +39185,19 @@
         <v>89</v>
       </c>
       <c r="L24">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="M24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O24" s="19">
         <v>0</v>
       </c>
       <c r="P24">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="Q24" t="s">
         <v>410</v>
@@ -39235,19 +39235,19 @@
         <v>89</v>
       </c>
       <c r="L25">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="M25">
         <v>0</v>
       </c>
       <c r="N25">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O25" s="19">
         <v>0</v>
       </c>
       <c r="P25">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="Q25" t="s">
         <v>410</v>
@@ -39285,10 +39285,10 @@
         <v>89</v>
       </c>
       <c r="L26">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="M26">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="N26">
         <v>0</v>
@@ -39297,7 +39297,7 @@
         <v>0</v>
       </c>
       <c r="P26">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="Q26" t="s">
         <v>410</v>
@@ -39335,19 +39335,19 @@
         <v>89</v>
       </c>
       <c r="L27">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M27">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="N27">
+        <v>4.5</v>
+      </c>
+      <c r="O27" s="19">
+        <v>0</v>
+      </c>
+      <c r="P27">
         <v>4</v>
-      </c>
-      <c r="O27" s="19">
-        <v>0</v>
-      </c>
-      <c r="P27">
-        <v>5</v>
       </c>
       <c r="Q27" t="s">
         <v>410</v>
@@ -39385,19 +39385,19 @@
         <v>89</v>
       </c>
       <c r="L28">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M28">
-        <v>23</v>
+        <v>20.5</v>
       </c>
       <c r="N28">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="O28" s="19">
         <v>4</v>
       </c>
       <c r="P28">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Q28" t="s">
         <v>410</v>
@@ -39538,19 +39538,19 @@
         <v>175</v>
       </c>
       <c r="L31">
-        <v>-4</v>
+        <v>-4.5</v>
       </c>
       <c r="M31">
         <v>4</v>
       </c>
       <c r="N31">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="O31" s="19">
         <v>2</v>
       </c>
       <c r="P31">
-        <v>-4</v>
+        <v>-4.5</v>
       </c>
       <c r="Q31" t="s">
         <v>410</v>
@@ -39588,19 +39588,19 @@
         <v>89</v>
       </c>
       <c r="L32">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="M32">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="N32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O32" s="19">
         <v>0</v>
       </c>
       <c r="P32">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="Q32" t="s">
         <v>410</v>
@@ -39641,10 +39641,10 @@
         <v>176</v>
       </c>
       <c r="L33">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M33">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N33">
         <v>6</v>
@@ -39653,7 +39653,7 @@
         <v>0</v>
       </c>
       <c r="P33">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q33" t="s">
         <v>410</v>
@@ -39694,10 +39694,10 @@
         <v>177</v>
       </c>
       <c r="L34">
-        <v>-3</v>
+        <v>3.5</v>
       </c>
       <c r="M34">
-        <v>5</v>
+        <v>11.5</v>
       </c>
       <c r="N34">
         <v>8</v>
@@ -39706,7 +39706,7 @@
         <v>2</v>
       </c>
       <c r="P34">
-        <v>-3</v>
+        <v>3.5</v>
       </c>
       <c r="Q34" t="s">
         <v>410</v>
@@ -39744,10 +39744,10 @@
         <v>89</v>
       </c>
       <c r="L35">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M35">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N35">
         <v>0</v>
@@ -39756,7 +39756,7 @@
         <v>0</v>
       </c>
       <c r="P35">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q35" t="s">
         <v>410</v>
@@ -39794,10 +39794,10 @@
         <v>89</v>
       </c>
       <c r="L36">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="M36">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="N36">
         <v>0</v>
@@ -39806,7 +39806,7 @@
         <v>0</v>
       </c>
       <c r="P36">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="Q36" t="s">
         <v>410</v>
@@ -39847,10 +39847,10 @@
         <v>178</v>
       </c>
       <c r="L37">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="M37">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="N37">
         <v>0</v>
@@ -39859,7 +39859,7 @@
         <v>0</v>
       </c>
       <c r="P37">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Q37" t="s">
         <v>410</v>
@@ -39897,10 +39897,10 @@
         <v>89</v>
       </c>
       <c r="L38">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M38">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="N38">
         <v>6</v>
@@ -39909,7 +39909,7 @@
         <v>2</v>
       </c>
       <c r="P38">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="Q38" t="s">
         <v>410</v>
@@ -39997,19 +39997,19 @@
         <v>89</v>
       </c>
       <c r="L40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M40">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="N40">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O40" s="19">
         <v>2</v>
       </c>
       <c r="P40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q40" t="s">
         <v>410</v>
@@ -40047,10 +40047,10 @@
         <v>89</v>
       </c>
       <c r="L41">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N41">
         <v>2</v>
@@ -40059,7 +40059,7 @@
         <v>2</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q41" t="s">
         <v>410</v>
@@ -40097,10 +40097,10 @@
         <v>89</v>
       </c>
       <c r="L42">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M42">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N42">
         <v>4</v>
@@ -40109,7 +40109,7 @@
         <v>0</v>
       </c>
       <c r="P42">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q42" t="s">
         <v>410</v>
@@ -40147,19 +40147,19 @@
         <v>89</v>
       </c>
       <c r="L43">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="M43">
-        <v>49</v>
+        <v>45.5</v>
       </c>
       <c r="N43">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="O43" s="19">
         <v>2</v>
       </c>
       <c r="P43">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="Q43" t="s">
         <v>410</v>
@@ -40300,19 +40300,19 @@
         <v>175</v>
       </c>
       <c r="L46">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="M46">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="N46">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O46" s="19">
         <v>2</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="Q46" t="s">
         <v>410</v>
@@ -40350,19 +40350,19 @@
         <v>89</v>
       </c>
       <c r="L47">
-        <v>-6</v>
+        <v>-6.5</v>
       </c>
       <c r="M47">
         <v>0</v>
       </c>
       <c r="N47">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="O47" s="19">
         <v>2</v>
       </c>
       <c r="P47">
-        <v>-6</v>
+        <v>-6.5</v>
       </c>
       <c r="Q47" t="s">
         <v>410</v>
@@ -40403,19 +40403,19 @@
         <v>176</v>
       </c>
       <c r="L48">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="M48">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N48">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O48" s="19">
         <v>0</v>
       </c>
       <c r="P48">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="Q48" t="s">
         <v>410</v>
@@ -40456,10 +40456,10 @@
         <v>177</v>
       </c>
       <c r="L49">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="M49">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="N49">
         <v>2</v>
@@ -40468,7 +40468,7 @@
         <v>2</v>
       </c>
       <c r="P49">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="Q49" t="s">
         <v>410</v>
@@ -40506,19 +40506,19 @@
         <v>89</v>
       </c>
       <c r="L50">
-        <v>-5</v>
+        <v>-7.5</v>
       </c>
       <c r="M50">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N50">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O50" s="19">
         <v>4</v>
       </c>
       <c r="P50">
-        <v>-5</v>
+        <v>-7.5</v>
       </c>
       <c r="Q50" t="s">
         <v>410</v>
@@ -40556,10 +40556,10 @@
         <v>89</v>
       </c>
       <c r="L51">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="M51">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="N51">
         <v>4</v>
@@ -40568,7 +40568,7 @@
         <v>2</v>
       </c>
       <c r="P51">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="Q51" t="s">
         <v>410</v>
@@ -40609,19 +40609,19 @@
         <v>178</v>
       </c>
       <c r="L52">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="M52">
         <v>11</v>
       </c>
       <c r="N52">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="O52" s="19">
         <v>4</v>
       </c>
       <c r="P52">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="Q52" t="s">
         <v>410</v>
@@ -40659,19 +40659,19 @@
         <v>89</v>
       </c>
       <c r="L53">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="M53">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N53">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="O53" s="19">
         <v>2</v>
       </c>
       <c r="P53">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="Q53" t="s">
         <v>410</v>
@@ -40759,10 +40759,10 @@
         <v>89</v>
       </c>
       <c r="L55">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="M55">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="N55">
         <v>0</v>
@@ -40771,7 +40771,7 @@
         <v>0</v>
       </c>
       <c r="P55">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="Q55" t="s">
         <v>410</v>
@@ -40809,10 +40809,10 @@
         <v>89</v>
       </c>
       <c r="L56">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="M56">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="N56">
         <v>2</v>
@@ -40821,7 +40821,7 @@
         <v>0</v>
       </c>
       <c r="P56">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Q56" t="s">
         <v>410</v>
@@ -40859,10 +40859,10 @@
         <v>89</v>
       </c>
       <c r="L57">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M57">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="N57">
         <v>8</v>
@@ -40871,7 +40871,7 @@
         <v>2</v>
       </c>
       <c r="P57">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Q57" t="s">
         <v>410</v>
@@ -40909,10 +40909,10 @@
         <v>89</v>
       </c>
       <c r="L58">
-        <v>25</v>
+        <v>20.5</v>
       </c>
       <c r="M58">
-        <v>37</v>
+        <v>32.5</v>
       </c>
       <c r="N58">
         <v>12</v>
@@ -40921,7 +40921,7 @@
         <v>6</v>
       </c>
       <c r="P58">
-        <v>25</v>
+        <v>20.5</v>
       </c>
       <c r="Q58" t="s">
         <v>410</v>
@@ -41059,19 +41059,19 @@
         <v>89</v>
       </c>
       <c r="L61">
-        <v>-4</v>
+        <v>-6.5</v>
       </c>
       <c r="M61">
         <v>3</v>
       </c>
       <c r="N61">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="O61" s="19">
         <v>0</v>
       </c>
       <c r="P61">
-        <v>-4</v>
+        <v>-6.5</v>
       </c>
       <c r="Q61" t="s">
         <v>410</v>
@@ -41112,19 +41112,19 @@
         <v>176</v>
       </c>
       <c r="L62">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="M62">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="N62">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O62" s="19">
         <v>4</v>
       </c>
       <c r="P62">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="Q62" t="s">
         <v>410</v>
@@ -41268,10 +41268,10 @@
         <v>6</v>
       </c>
       <c r="M65">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="N65">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="O65" s="19">
         <v>2</v>
@@ -41318,19 +41318,19 @@
         <v>178</v>
       </c>
       <c r="L66">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="M66">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="N66">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="O66" s="19">
         <v>2</v>
       </c>
       <c r="P66">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="Q66" t="s">
         <v>410</v>
@@ -41418,19 +41418,19 @@
         <v>89</v>
       </c>
       <c r="L68">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="M68">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="N68">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="O68" s="19">
         <v>2</v>
       </c>
       <c r="P68">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="Q68" t="s">
         <v>410</v>
@@ -41468,19 +41468,19 @@
         <v>89</v>
       </c>
       <c r="L69">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="M69">
         <v>0</v>
       </c>
       <c r="N69">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O69" s="19">
         <v>2</v>
       </c>
       <c r="P69">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="Q69" t="s">
         <v>410</v>
@@ -41518,19 +41518,19 @@
         <v>89</v>
       </c>
       <c r="L70">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="M70">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="N70">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="O70" s="19">
         <v>2</v>
       </c>
       <c r="P70">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="Q70" t="s">
         <v>410</v>
@@ -41568,19 +41568,19 @@
         <v>89</v>
       </c>
       <c r="L71">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="M71">
-        <v>29</v>
+        <v>25.5</v>
       </c>
       <c r="N71">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="O71" s="19">
         <v>6</v>
       </c>
       <c r="P71">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Q71" t="s">
         <v>410</v>
@@ -41721,10 +41721,10 @@
         <v>175</v>
       </c>
       <c r="L74">
-        <v>-2</v>
+        <v>-2.5</v>
       </c>
       <c r="M74">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N74">
         <v>6</v>
@@ -41733,7 +41733,7 @@
         <v>4</v>
       </c>
       <c r="P74">
-        <v>-2</v>
+        <v>-2.5</v>
       </c>
       <c r="Q74" t="s">
         <v>410</v>
@@ -41824,19 +41824,19 @@
         <v>176</v>
       </c>
       <c r="L76">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="M76">
-        <v>27</v>
+        <v>24.5</v>
       </c>
       <c r="N76">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="O76" s="19">
         <v>4</v>
       </c>
       <c r="P76">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="Q76" t="s">
         <v>410</v>
@@ -41877,19 +41877,19 @@
         <v>177</v>
       </c>
       <c r="L77">
-        <v>-2</v>
+        <v>-4.5</v>
       </c>
       <c r="M77">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="N77">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O77" s="19">
         <v>6</v>
       </c>
       <c r="P77">
-        <v>-2</v>
+        <v>-4.5</v>
       </c>
       <c r="Q77" t="s">
         <v>410</v>
@@ -41927,10 +41927,10 @@
         <v>89</v>
       </c>
       <c r="L78">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="M78">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="N78">
         <v>8</v>
@@ -41939,7 +41939,7 @@
         <v>2</v>
       </c>
       <c r="P78">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="Q78" t="s">
         <v>410</v>
@@ -41977,10 +41977,10 @@
         <v>89</v>
       </c>
       <c r="L79">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="M79">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="N79">
         <v>4</v>
@@ -41989,7 +41989,7 @@
         <v>2</v>
       </c>
       <c r="P79">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Q79" t="s">
         <v>410</v>
@@ -42030,19 +42030,19 @@
         <v>178</v>
       </c>
       <c r="L80">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="M80">
-        <v>22</v>
+        <v>29.5</v>
       </c>
       <c r="N80">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="O80" s="19">
         <v>2</v>
       </c>
       <c r="P80">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="Q80" t="s">
         <v>410</v>
@@ -42130,10 +42130,10 @@
         <v>89</v>
       </c>
       <c r="L82">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="M82">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="N82">
         <v>6</v>
@@ -42142,7 +42142,7 @@
         <v>4</v>
       </c>
       <c r="P82">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="Q82" t="s">
         <v>410</v>
@@ -42180,10 +42180,10 @@
         <v>89</v>
       </c>
       <c r="L83">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M83">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N83">
         <v>0</v>
@@ -42192,7 +42192,7 @@
         <v>0</v>
       </c>
       <c r="P83">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Q83" t="s">
         <v>410</v>
@@ -42230,10 +42230,10 @@
         <v>89</v>
       </c>
       <c r="L84">
-        <v>-3</v>
+        <v>-3.5</v>
       </c>
       <c r="M84">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N84">
         <v>4</v>
@@ -42242,7 +42242,7 @@
         <v>2</v>
       </c>
       <c r="P84">
-        <v>-3</v>
+        <v>-3.5</v>
       </c>
       <c r="Q84" t="s">
         <v>410</v>
@@ -42280,19 +42280,19 @@
         <v>89</v>
       </c>
       <c r="L85">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M85">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="N85">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O85" s="19">
         <v>4</v>
       </c>
       <c r="P85">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q85" t="s">
         <v>410</v>
@@ -42433,10 +42433,10 @@
         <v>175</v>
       </c>
       <c r="L88">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M88">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="N88">
         <v>4</v>
@@ -42445,7 +42445,7 @@
         <v>0</v>
       </c>
       <c r="P88">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Q88" t="s">
         <v>410</v>
@@ -42483,19 +42483,19 @@
         <v>89</v>
       </c>
       <c r="L89">
-        <v>-4</v>
+        <v>-4.5</v>
       </c>
       <c r="M89">
         <v>0</v>
       </c>
       <c r="N89">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O89" s="19">
         <v>2</v>
       </c>
       <c r="P89">
-        <v>-4</v>
+        <v>-4.5</v>
       </c>
       <c r="Q89" t="s">
         <v>410</v>
@@ -42536,10 +42536,10 @@
         <v>176</v>
       </c>
       <c r="L90">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="M90">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N90">
         <v>12</v>
@@ -42548,7 +42548,7 @@
         <v>4</v>
       </c>
       <c r="P90">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="Q90" t="s">
         <v>410</v>
@@ -42589,19 +42589,19 @@
         <v>177</v>
       </c>
       <c r="L91">
-        <v>19</v>
+        <v>20.5</v>
       </c>
       <c r="M91">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N91">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="O91" s="19">
         <v>2</v>
       </c>
       <c r="P91">
-        <v>19</v>
+        <v>20.5</v>
       </c>
       <c r="Q91" t="s">
         <v>410</v>
@@ -42639,19 +42639,19 @@
         <v>89</v>
       </c>
       <c r="L92">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="M92">
-        <v>24</v>
+        <v>22.5</v>
       </c>
       <c r="N92">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O92" s="19">
         <v>0</v>
       </c>
       <c r="P92">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="Q92" t="s">
         <v>410</v>
@@ -42742,19 +42742,19 @@
         <v>178</v>
       </c>
       <c r="L94">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="M94">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="N94">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O94" s="19">
         <v>4</v>
       </c>
       <c r="P94">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="Q94" t="s">
         <v>410</v>
@@ -42792,10 +42792,10 @@
         <v>89</v>
       </c>
       <c r="L95">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="M95">
-        <v>22</v>
+        <v>20.5</v>
       </c>
       <c r="N95">
         <v>2</v>
@@ -42804,7 +42804,7 @@
         <v>0</v>
       </c>
       <c r="P95">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="Q95" t="s">
         <v>410</v>
@@ -42842,10 +42842,10 @@
         <v>89</v>
       </c>
       <c r="L96">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="M96">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="N96">
         <v>2</v>
@@ -42854,7 +42854,7 @@
         <v>2</v>
       </c>
       <c r="P96">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="Q96" t="s">
         <v>410</v>
@@ -42892,10 +42892,10 @@
         <v>89</v>
       </c>
       <c r="L97">
-        <v>-1</v>
+        <v>-1.5</v>
       </c>
       <c r="M97">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N97">
         <v>2</v>
@@ -42904,7 +42904,7 @@
         <v>2</v>
       </c>
       <c r="P97">
-        <v>-1</v>
+        <v>-1.5</v>
       </c>
       <c r="Q97" t="s">
         <v>410</v>
@@ -42992,10 +42992,10 @@
         <v>89</v>
       </c>
       <c r="L99">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="M99">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="N99">
         <v>6</v>
@@ -43004,7 +43004,7 @@
         <v>4</v>
       </c>
       <c r="P99">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="Q99" t="s">
         <v>410</v>
@@ -43148,10 +43148,10 @@
         <v>7</v>
       </c>
       <c r="M102">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="N102">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="O102" s="19">
         <v>4</v>
@@ -43195,19 +43195,19 @@
         <v>89</v>
       </c>
       <c r="L103">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="M103">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N103">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="O103" s="19">
         <v>0</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="Q103" t="s">
         <v>410</v>
@@ -43248,19 +43248,19 @@
         <v>176</v>
       </c>
       <c r="L104">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M104">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="N104">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="O104" s="19">
         <v>4</v>
       </c>
       <c r="P104">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q104" t="s">
         <v>410</v>
@@ -43301,19 +43301,19 @@
         <v>177</v>
       </c>
       <c r="L105">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M105">
         <v>22</v>
       </c>
       <c r="N105">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O105" s="19">
         <v>2</v>
       </c>
       <c r="P105">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q105" t="s">
         <v>410</v>
@@ -43351,19 +43351,19 @@
         <v>89</v>
       </c>
       <c r="L106">
-        <v>-4</v>
+        <v>-6.5</v>
       </c>
       <c r="M106">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N106">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O106" s="19">
         <v>2</v>
       </c>
       <c r="P106">
-        <v>-4</v>
+        <v>-6.5</v>
       </c>
       <c r="Q106" t="s">
         <v>410</v>
@@ -43401,10 +43401,10 @@
         <v>89</v>
       </c>
       <c r="L107">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M107">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N107">
         <v>2</v>
@@ -43413,7 +43413,7 @@
         <v>0</v>
       </c>
       <c r="P107">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q107" t="s">
         <v>410</v>
@@ -43454,10 +43454,10 @@
         <v>178</v>
       </c>
       <c r="L108">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="M108">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="N108">
         <v>6</v>
@@ -43466,7 +43466,7 @@
         <v>2</v>
       </c>
       <c r="P108">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="Q108" t="s">
         <v>410</v>
@@ -43504,19 +43504,19 @@
         <v>89</v>
       </c>
       <c r="L109">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="M109">
         <v>2</v>
       </c>
       <c r="N109">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="O109" s="19">
         <v>0</v>
       </c>
       <c r="P109">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="Q109" t="s">
         <v>410</v>
@@ -43554,19 +43554,19 @@
         <v>89</v>
       </c>
       <c r="L110">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="M110">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="N110">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O110" s="19">
         <v>4</v>
       </c>
       <c r="P110">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="Q110" t="s">
         <v>410</v>
@@ -43654,10 +43654,10 @@
         <v>89</v>
       </c>
       <c r="L112">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M112">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N112">
         <v>2</v>
@@ -43666,7 +43666,7 @@
         <v>2</v>
       </c>
       <c r="P112">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q112" t="s">
         <v>410</v>
@@ -43704,10 +43704,10 @@
         <v>89</v>
       </c>
       <c r="L113">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="M113">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="N113">
         <v>2</v>
@@ -43716,7 +43716,7 @@
         <v>2</v>
       </c>
       <c r="P113">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Q113" t="s">
         <v>410</v>
@@ -43857,10 +43857,10 @@
         <v>175</v>
       </c>
       <c r="L116">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="M116">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="N116">
         <v>6</v>
@@ -43869,7 +43869,7 @@
         <v>2</v>
       </c>
       <c r="P116">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="Q116" t="s">
         <v>410</v>
@@ -43907,19 +43907,19 @@
         <v>89</v>
       </c>
       <c r="L117">
-        <v>3</v>
+        <v>-0.5</v>
       </c>
       <c r="M117">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="N117">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O117" s="19">
         <v>0</v>
       </c>
       <c r="P117">
-        <v>3</v>
+        <v>-0.5</v>
       </c>
       <c r="Q117" t="s">
         <v>410</v>
@@ -43960,10 +43960,10 @@
         <v>176</v>
       </c>
       <c r="L118">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="M118">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="N118">
         <v>0</v>
@@ -43972,7 +43972,7 @@
         <v>0</v>
       </c>
       <c r="P118">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="Q118" t="s">
         <v>410</v>
@@ -44013,19 +44013,19 @@
         <v>177</v>
       </c>
       <c r="L119">
+        <v>20.5</v>
+      </c>
+      <c r="M119">
         <v>23</v>
       </c>
-      <c r="M119">
-        <v>25</v>
-      </c>
       <c r="N119">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="O119" s="19">
         <v>0</v>
       </c>
       <c r="P119">
-        <v>23</v>
+        <v>20.5</v>
       </c>
       <c r="Q119" t="s">
         <v>410</v>
@@ -44063,19 +44063,19 @@
         <v>89</v>
       </c>
       <c r="L120">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="M120">
         <v>8</v>
       </c>
       <c r="N120">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="O120" s="19">
         <v>0</v>
       </c>
       <c r="P120">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="Q120" t="s">
         <v>410</v>
@@ -44113,19 +44113,19 @@
         <v>89</v>
       </c>
       <c r="L121">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="M121">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N121">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="O121" s="19">
         <v>0</v>
       </c>
       <c r="P121">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="Q121" t="s">
         <v>410</v>
@@ -44166,19 +44166,19 @@
         <v>178</v>
       </c>
       <c r="L122">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="M122">
-        <v>24</v>
+        <v>18.5</v>
       </c>
       <c r="N122">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="O122" s="19">
         <v>0</v>
       </c>
       <c r="P122">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="Q122" t="s">
         <v>410</v>
@@ -44216,10 +44216,10 @@
         <v>89</v>
       </c>
       <c r="L123">
-        <v>23</v>
+        <v>21.5</v>
       </c>
       <c r="M123">
-        <v>23</v>
+        <v>21.5</v>
       </c>
       <c r="N123">
         <v>0</v>
@@ -44228,7 +44228,7 @@
         <v>0</v>
       </c>
       <c r="P123">
-        <v>23</v>
+        <v>21.5</v>
       </c>
       <c r="Q123" t="s">
         <v>410</v>
@@ -44266,19 +44266,19 @@
         <v>89</v>
       </c>
       <c r="L124">
-        <v>1</v>
+        <v>-4.5</v>
       </c>
       <c r="M124">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="N124">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="O124" s="19">
         <v>0</v>
       </c>
       <c r="P124">
-        <v>1</v>
+        <v>-4.5</v>
       </c>
       <c r="Q124" t="s">
         <v>410</v>
@@ -44316,10 +44316,10 @@
         <v>89</v>
       </c>
       <c r="L125">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="M125">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="N125">
         <v>6</v>
@@ -44328,7 +44328,7 @@
         <v>2</v>
       </c>
       <c r="P125">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="Q125" t="s">
         <v>410</v>
@@ -44366,19 +44366,19 @@
         <v>89</v>
       </c>
       <c r="L126">
-        <v>28</v>
+        <v>26.5</v>
       </c>
       <c r="M126">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="N126">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O126" s="19">
         <v>0</v>
       </c>
       <c r="P126">
-        <v>28</v>
+        <v>26.5</v>
       </c>
       <c r="Q126" t="s">
         <v>410</v>
@@ -44416,19 +44416,19 @@
         <v>89</v>
       </c>
       <c r="L127">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="M127">
-        <v>49</v>
+        <v>42.5</v>
       </c>
       <c r="N127">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O127" s="19">
         <v>0</v>
       </c>
       <c r="P127">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="Q127" t="s">
         <v>410</v>
@@ -44619,19 +44619,19 @@
         <v>175</v>
       </c>
       <c r="L131">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M131">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="N131">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O131" s="19">
         <v>2</v>
       </c>
       <c r="P131">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Q131" t="s">
         <v>410</v>
@@ -44669,10 +44669,10 @@
         <v>89</v>
       </c>
       <c r="L132">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M132">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N132">
         <v>2</v>
@@ -44681,7 +44681,7 @@
         <v>0</v>
       </c>
       <c r="P132">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q132" t="s">
         <v>410</v>
@@ -44725,10 +44725,10 @@
         <v>9</v>
       </c>
       <c r="M133">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="N133">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O133" s="19">
         <v>2</v>
@@ -44775,19 +44775,19 @@
         <v>177</v>
       </c>
       <c r="L134">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="M134">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N134">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="O134" s="19">
         <v>2</v>
       </c>
       <c r="P134">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="Q134" t="s">
         <v>410</v>
@@ -44825,10 +44825,10 @@
         <v>89</v>
       </c>
       <c r="L135">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="M135">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="N135">
         <v>0</v>
@@ -44837,7 +44837,7 @@
         <v>0</v>
       </c>
       <c r="P135">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Q135" t="s">
         <v>410</v>
@@ -44875,10 +44875,10 @@
         <v>89</v>
       </c>
       <c r="L136">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M136">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N136">
         <v>2</v>
@@ -44887,7 +44887,7 @@
         <v>0</v>
       </c>
       <c r="P136">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Q136" t="s">
         <v>410</v>
@@ -44928,10 +44928,10 @@
         <v>178</v>
       </c>
       <c r="L137">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="M137">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="N137">
         <v>8</v>
@@ -44940,7 +44940,7 @@
         <v>2</v>
       </c>
       <c r="P137">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="Q137" t="s">
         <v>410</v>
@@ -44978,10 +44978,10 @@
         <v>89</v>
       </c>
       <c r="L138">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M138">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N138">
         <v>2</v>
@@ -44990,7 +44990,7 @@
         <v>0</v>
       </c>
       <c r="P138">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Q138" t="s">
         <v>410</v>
@@ -45028,19 +45028,19 @@
         <v>89</v>
       </c>
       <c r="L139">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M139">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="N139">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="O139" s="19">
         <v>0</v>
       </c>
       <c r="P139">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q139" t="s">
         <v>410</v>
@@ -45078,19 +45078,19 @@
         <v>89</v>
       </c>
       <c r="L140">
-        <v>-1</v>
+        <v>-1.5</v>
       </c>
       <c r="M140">
         <v>3</v>
       </c>
       <c r="N140">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O140" s="19">
         <v>0</v>
       </c>
       <c r="P140">
-        <v>-1</v>
+        <v>-1.5</v>
       </c>
       <c r="Q140" t="s">
         <v>410</v>
@@ -45128,10 +45128,10 @@
         <v>89</v>
       </c>
       <c r="L141">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="M141">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="N141">
         <v>0</v>
@@ -45140,7 +45140,7 @@
         <v>0</v>
       </c>
       <c r="P141">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Q141" t="s">
         <v>410</v>
@@ -45178,19 +45178,19 @@
         <v>89</v>
       </c>
       <c r="L142">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="M142">
         <v>29</v>
       </c>
       <c r="N142">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="O142" s="19">
         <v>4</v>
       </c>
       <c r="P142">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="Q142" t="s">
         <v>410</v>
@@ -45331,10 +45331,10 @@
         <v>175</v>
       </c>
       <c r="L145">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="M145">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="N145">
         <v>4</v>
@@ -45343,7 +45343,7 @@
         <v>4</v>
       </c>
       <c r="P145">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Q145" t="s">
         <v>410</v>
@@ -45381,10 +45381,10 @@
         <v>89</v>
       </c>
       <c r="L146">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="M146">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="N146">
         <v>2</v>
@@ -45393,7 +45393,7 @@
         <v>0</v>
       </c>
       <c r="P146">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="Q146" t="s">
         <v>410</v>
@@ -45434,10 +45434,10 @@
         <v>176</v>
       </c>
       <c r="L147">
-        <v>19</v>
+        <v>12.5</v>
       </c>
       <c r="M147">
-        <v>23</v>
+        <v>16.5</v>
       </c>
       <c r="N147">
         <v>4</v>
@@ -45446,7 +45446,7 @@
         <v>0</v>
       </c>
       <c r="P147">
-        <v>19</v>
+        <v>12.5</v>
       </c>
       <c r="Q147" t="s">
         <v>410</v>
@@ -45487,19 +45487,19 @@
         <v>177</v>
       </c>
       <c r="L148">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M148">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="N148">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O148" s="19">
         <v>0</v>
       </c>
       <c r="P148">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q148" t="s">
         <v>410</v>
@@ -45590,19 +45590,19 @@
         <v>178</v>
       </c>
       <c r="L150">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="M150">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="N150">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="O150" s="19">
         <v>0</v>
       </c>
       <c r="P150">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q150" t="s">
         <v>410</v>
@@ -45640,19 +45640,19 @@
         <v>89</v>
       </c>
       <c r="L151">
-        <v>-4</v>
+        <v>-6.5</v>
       </c>
       <c r="M151">
         <v>3</v>
       </c>
       <c r="N151">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="O151" s="19">
         <v>4</v>
       </c>
       <c r="P151">
-        <v>-4</v>
+        <v>-6.5</v>
       </c>
       <c r="Q151" t="s">
         <v>410</v>
@@ -45740,19 +45740,19 @@
         <v>89</v>
       </c>
       <c r="L153">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="M153">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N153">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="O153" s="19">
         <v>0</v>
       </c>
       <c r="P153">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="Q153" t="s">
         <v>410</v>
@@ -45790,19 +45790,19 @@
         <v>89</v>
       </c>
       <c r="L154">
-        <v>-1</v>
+        <v>0.5</v>
       </c>
       <c r="M154">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N154">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="O154" s="19">
         <v>0</v>
       </c>
       <c r="P154">
-        <v>-1</v>
+        <v>0.5</v>
       </c>
       <c r="Q154" t="s">
         <v>410</v>
@@ -45840,10 +45840,10 @@
         <v>89</v>
       </c>
       <c r="L155">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M155">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N155">
         <v>4</v>
@@ -45852,7 +45852,7 @@
         <v>0</v>
       </c>
       <c r="P155">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Q155" t="s">
         <v>410</v>
@@ -45890,19 +45890,19 @@
         <v>89</v>
       </c>
       <c r="L156">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="M156">
-        <v>30</v>
+        <v>23.5</v>
       </c>
       <c r="N156">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="O156" s="19">
         <v>2</v>
       </c>
       <c r="P156">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="Q156" t="s">
         <v>410</v>
@@ -46043,10 +46043,10 @@
         <v>175</v>
       </c>
       <c r="L159">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="M159">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="N159">
         <v>0</v>
@@ -46055,7 +46055,7 @@
         <v>0</v>
       </c>
       <c r="P159">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="Q159" t="s">
         <v>410</v>
@@ -46093,19 +46093,19 @@
         <v>89</v>
       </c>
       <c r="L160">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="M160">
-        <v>11</v>
+        <v>7.5</v>
       </c>
       <c r="N160">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O160" s="19">
         <v>0</v>
       </c>
       <c r="P160">
-        <v>5</v>
+        <v>0.5</v>
       </c>
       <c r="Q160" t="s">
         <v>410</v>
@@ -46146,19 +46146,19 @@
         <v>176</v>
       </c>
       <c r="L161">
-        <v>39</v>
+        <v>30.5</v>
       </c>
       <c r="M161">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="N161">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O161" s="19">
         <v>0</v>
       </c>
       <c r="P161">
-        <v>39</v>
+        <v>30.5</v>
       </c>
       <c r="Q161" t="s">
         <v>410</v>
@@ -46199,19 +46199,19 @@
         <v>177</v>
       </c>
       <c r="L162">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="M162">
-        <v>22</v>
+        <v>26.5</v>
       </c>
       <c r="N162">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="O162" s="19">
         <v>2</v>
       </c>
       <c r="P162">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q162" t="s">
         <v>410</v>
@@ -46249,19 +46249,19 @@
         <v>89</v>
       </c>
       <c r="L163">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="M163">
-        <v>6</v>
+        <v>9.5</v>
       </c>
       <c r="N163">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O163" s="19">
         <v>0</v>
       </c>
       <c r="P163">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="Q163" t="s">
         <v>410</v>
@@ -46299,10 +46299,10 @@
         <v>89</v>
       </c>
       <c r="L164">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="M164">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="N164">
         <v>0</v>
@@ -46311,7 +46311,7 @@
         <v>0</v>
       </c>
       <c r="P164">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="Q164" t="s">
         <v>410</v>
@@ -46352,19 +46352,19 @@
         <v>178</v>
       </c>
       <c r="L165">
-        <v>27</v>
+        <v>23.5</v>
       </c>
       <c r="M165">
-        <v>35</v>
+        <v>32.5</v>
       </c>
       <c r="N165">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O165" s="19">
         <v>0</v>
       </c>
       <c r="P165">
-        <v>27</v>
+        <v>23.5</v>
       </c>
       <c r="Q165" t="s">
         <v>410</v>
@@ -46402,19 +46402,19 @@
         <v>89</v>
       </c>
       <c r="L166">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M166">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="N166">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="O166" s="19">
         <v>0</v>
       </c>
       <c r="P166">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q166" t="s">
         <v>410</v>
@@ -46452,19 +46452,19 @@
         <v>89</v>
       </c>
       <c r="L167">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M167">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="N167">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="O167" s="19">
         <v>0</v>
       </c>
       <c r="P167">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q167" t="s">
         <v>410</v>
@@ -46502,10 +46502,10 @@
         <v>89</v>
       </c>
       <c r="L168">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M168">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N168">
         <v>0</v>
@@ -46514,7 +46514,7 @@
         <v>0</v>
       </c>
       <c r="P168">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q168" t="s">
         <v>410</v>
@@ -46552,19 +46552,19 @@
         <v>89</v>
       </c>
       <c r="L169">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M169">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="N169">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="O169" s="19">
         <v>2</v>
       </c>
       <c r="P169">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q169" t="s">
         <v>410</v>
@@ -46602,19 +46602,19 @@
         <v>89</v>
       </c>
       <c r="L170">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="M170">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N170">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="O170" s="19">
         <v>0</v>
       </c>
       <c r="P170">
-        <v>9</v>
+        <v>7.5</v>
       </c>
       <c r="Q170" t="s">
         <v>410</v>
@@ -46752,19 +46752,19 @@
         <v>89</v>
       </c>
       <c r="L173">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="M173">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="N173">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="O173" s="19">
         <v>2</v>
       </c>
       <c r="P173">
-        <v>-7</v>
+        <v>-9</v>
       </c>
       <c r="Q173" t="s">
         <v>410</v>
@@ -46805,10 +46805,10 @@
         <v>176</v>
       </c>
       <c r="L174">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="M174">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="N174">
         <v>0</v>
@@ -46817,7 +46817,7 @@
         <v>0</v>
       </c>
       <c r="P174">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="Q174" t="s">
         <v>410</v>
@@ -46858,19 +46858,19 @@
         <v>177</v>
       </c>
       <c r="L175">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="M175">
-        <v>23</v>
+        <v>22.5</v>
       </c>
       <c r="N175">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O175" s="19">
         <v>2</v>
       </c>
       <c r="P175">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="Q175" t="s">
         <v>410</v>
@@ -46908,19 +46908,19 @@
         <v>89</v>
       </c>
       <c r="L176">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="M176">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N176">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O176" s="19">
         <v>2</v>
       </c>
       <c r="P176">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="Q176" t="s">
         <v>410</v>
@@ -47011,19 +47011,19 @@
         <v>178</v>
       </c>
       <c r="L178">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="M178">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N178">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="O178" s="19">
         <v>2</v>
       </c>
       <c r="P178">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Q178" t="s">
         <v>410</v>
@@ -47061,10 +47061,10 @@
         <v>89</v>
       </c>
       <c r="L179">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="M179">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="N179">
         <v>4</v>
@@ -47073,7 +47073,7 @@
         <v>0</v>
       </c>
       <c r="P179">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="Q179" t="s">
         <v>410</v>
@@ -47161,10 +47161,10 @@
         <v>89</v>
       </c>
       <c r="L181">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="M181">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="N181">
         <v>0</v>
@@ -47173,7 +47173,7 @@
         <v>0</v>
       </c>
       <c r="P181">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="Q181" t="s">
         <v>410</v>
@@ -47211,10 +47211,10 @@
         <v>89</v>
       </c>
       <c r="L182">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M182">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N182">
         <v>2</v>
@@ -47223,7 +47223,7 @@
         <v>2</v>
       </c>
       <c r="P182">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="Q182" t="s">
         <v>410</v>
@@ -47261,19 +47261,19 @@
         <v>89</v>
       </c>
       <c r="L183">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M183">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N183">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O183" s="19">
         <v>0</v>
       </c>
       <c r="P183">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="Q183" t="s">
         <v>410</v>
@@ -47311,19 +47311,19 @@
         <v>89</v>
       </c>
       <c r="L184">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="M184">
-        <v>25</v>
+        <v>23.5</v>
       </c>
       <c r="N184">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="O184" s="19">
         <v>2</v>
       </c>
       <c r="P184">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Q184" t="s">
         <v>410</v>
@@ -47464,11 +47464,11 @@
         <v>175</v>
       </c>
       <c r="L187">
+        <v>18</v>
+      </c>
+      <c r="M187">
         <v>20</v>
       </c>
-      <c r="M187">
-        <v>22</v>
-      </c>
       <c r="N187">
         <v>2</v>
       </c>
@@ -47476,7 +47476,7 @@
         <v>0</v>
       </c>
       <c r="P187">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Q187" t="s">
         <v>410</v>
@@ -47514,19 +47514,19 @@
         <v>89</v>
       </c>
       <c r="L188">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M188">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="N188">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="O188" s="19">
         <v>0</v>
       </c>
       <c r="P188">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q188" t="s">
         <v>410</v>
@@ -47567,10 +47567,10 @@
         <v>176</v>
       </c>
       <c r="L189">
-        <v>35</v>
+        <v>33.5</v>
       </c>
       <c r="M189">
-        <v>41</v>
+        <v>39.5</v>
       </c>
       <c r="N189">
         <v>6</v>
@@ -47579,7 +47579,7 @@
         <v>0</v>
       </c>
       <c r="P189">
-        <v>35</v>
+        <v>33.5</v>
       </c>
       <c r="Q189" t="s">
         <v>410</v>
@@ -47617,19 +47617,19 @@
         <v>89</v>
       </c>
       <c r="L190">
-        <v>-1</v>
+        <v>-1.5</v>
       </c>
       <c r="M190">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="N190">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O190" s="19">
         <v>2</v>
       </c>
       <c r="P190">
-        <v>-1</v>
+        <v>-1.5</v>
       </c>
       <c r="Q190" t="s">
         <v>410</v>
@@ -47667,19 +47667,19 @@
         <v>89</v>
       </c>
       <c r="L191">
-        <v>3</v>
+        <v>-0.5</v>
       </c>
       <c r="M191">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="N191">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O191" s="19">
         <v>0</v>
       </c>
       <c r="P191">
-        <v>3</v>
+        <v>-0.5</v>
       </c>
       <c r="Q191" t="s">
         <v>410</v>
@@ -47720,19 +47720,19 @@
         <v>178</v>
       </c>
       <c r="L192">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="M192">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="N192">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="O192" s="19">
         <v>0</v>
       </c>
       <c r="P192">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="Q192" t="s">
         <v>410</v>
@@ -47770,10 +47770,10 @@
         <v>89</v>
       </c>
       <c r="L193">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="M193">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="N193">
         <v>0</v>
@@ -47782,7 +47782,7 @@
         <v>0</v>
       </c>
       <c r="P193">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Q193" t="s">
         <v>410</v>
@@ -47920,10 +47920,10 @@
         <v>89</v>
       </c>
       <c r="L196">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M196">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N196">
         <v>0</v>
@@ -47932,7 +47932,7 @@
         <v>0</v>
       </c>
       <c r="P196">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q196" t="s">
         <v>410</v>
@@ -47970,19 +47970,19 @@
         <v>89</v>
       </c>
       <c r="L197">
-        <v>22</v>
+        <v>13.5</v>
       </c>
       <c r="M197">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="N197">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O197" s="19">
         <v>0</v>
       </c>
       <c r="P197">
-        <v>22</v>
+        <v>13.5</v>
       </c>
       <c r="Q197" t="s">
         <v>410</v>
@@ -48020,19 +48020,19 @@
         <v>89</v>
       </c>
       <c r="L198">
-        <v>22</v>
+        <v>13.5</v>
       </c>
       <c r="M198">
-        <v>30</v>
+        <v>22.5</v>
       </c>
       <c r="N198">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O198" s="19">
         <v>2</v>
       </c>
       <c r="P198">
-        <v>22</v>
+        <v>13.5</v>
       </c>
       <c r="Q198" t="s">
         <v>410</v>
@@ -48173,10 +48173,10 @@
         <v>175</v>
       </c>
       <c r="L201">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M201">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N201">
         <v>6</v>
@@ -48185,7 +48185,7 @@
         <v>4</v>
       </c>
       <c r="P201">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q201" t="s">
         <v>410</v>
@@ -48223,10 +48223,10 @@
         <v>89</v>
       </c>
       <c r="L202">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M202">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N202">
         <v>4</v>
@@ -48235,7 +48235,7 @@
         <v>2</v>
       </c>
       <c r="P202">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q202" t="s">
         <v>410</v>
@@ -48276,10 +48276,10 @@
         <v>176</v>
       </c>
       <c r="L203">
-        <v>45</v>
+        <v>39.5</v>
       </c>
       <c r="M203">
-        <v>47</v>
+        <v>41.5</v>
       </c>
       <c r="N203">
         <v>2</v>
@@ -48288,7 +48288,7 @@
         <v>2</v>
       </c>
       <c r="P203">
-        <v>45</v>
+        <v>39.5</v>
       </c>
       <c r="Q203" t="s">
         <v>410</v>
@@ -48326,10 +48326,10 @@
         <v>89</v>
       </c>
       <c r="L204">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="M204">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="N204">
         <v>0</v>
@@ -48338,7 +48338,7 @@
         <v>0</v>
       </c>
       <c r="P204">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="Q204" t="s">
         <v>410</v>
@@ -48379,10 +48379,10 @@
         <v>177</v>
       </c>
       <c r="L205">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="M205">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="N205">
         <v>4</v>
@@ -48391,7 +48391,7 @@
         <v>2</v>
       </c>
       <c r="P205">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="Q205" t="s">
         <v>410</v>
@@ -48429,19 +48429,19 @@
         <v>89</v>
       </c>
       <c r="L206">
-        <v>0</v>
+        <v>-3.5</v>
       </c>
       <c r="M206">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N206">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="O206" s="19">
         <v>0</v>
       </c>
       <c r="P206">
-        <v>0</v>
+        <v>-3.5</v>
       </c>
       <c r="Q206" t="s">
         <v>410</v>
@@ -48479,10 +48479,10 @@
         <v>89</v>
       </c>
       <c r="L207">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="M207">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="N207">
         <v>2</v>
@@ -48491,7 +48491,7 @@
         <v>0</v>
       </c>
       <c r="P207">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="Q207" t="s">
         <v>410</v>
@@ -48579,19 +48579,19 @@
         <v>89</v>
       </c>
       <c r="L209">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M209">
-        <v>12</v>
+        <v>9.5</v>
       </c>
       <c r="N209">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O209" s="19">
         <v>0</v>
       </c>
       <c r="P209">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q209" t="s">
         <v>410</v>
@@ -48679,10 +48679,10 @@
         <v>89</v>
       </c>
       <c r="L211">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M211">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N211">
         <v>0</v>
@@ -48691,7 +48691,7 @@
         <v>0</v>
       </c>
       <c r="P211">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q211" t="s">
         <v>410</v>
@@ -48729,10 +48729,10 @@
         <v>89</v>
       </c>
       <c r="L212">
-        <v>27</v>
+        <v>24.5</v>
       </c>
       <c r="M212">
-        <v>31</v>
+        <v>28.5</v>
       </c>
       <c r="N212">
         <v>4</v>
@@ -48741,7 +48741,7 @@
         <v>4</v>
       </c>
       <c r="P212">
-        <v>27</v>
+        <v>24.5</v>
       </c>
       <c r="Q212" t="s">
         <v>410</v>
@@ -48882,19 +48882,19 @@
         <v>175</v>
       </c>
       <c r="L215">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="M215">
-        <v>23</v>
+        <v>21.5</v>
       </c>
       <c r="N215">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O215" s="19">
         <v>2</v>
       </c>
       <c r="P215">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="Q215" t="s">
         <v>410</v>
@@ -48932,19 +48932,19 @@
         <v>89</v>
       </c>
       <c r="L216">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M216">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="N216">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="O216" s="19">
         <v>2</v>
       </c>
       <c r="P216">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q216" t="s">
         <v>410</v>
@@ -48985,19 +48985,19 @@
         <v>176</v>
       </c>
       <c r="L217">
-        <v>25</v>
+        <v>20.5</v>
       </c>
       <c r="M217">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="N217">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="O217" s="19">
         <v>0</v>
       </c>
       <c r="P217">
-        <v>25</v>
+        <v>20.5</v>
       </c>
       <c r="Q217" t="s">
         <v>410</v>
@@ -49088,10 +49088,10 @@
         <v>89</v>
       </c>
       <c r="L219">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="M219">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="N219">
         <v>0</v>
@@ -49100,7 +49100,7 @@
         <v>0</v>
       </c>
       <c r="P219">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="Q219" t="s">
         <v>410</v>
@@ -49138,19 +49138,19 @@
         <v>89</v>
       </c>
       <c r="L220">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="M220">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="N220">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O220" s="19">
         <v>0</v>
       </c>
       <c r="P220">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="Q220" t="s">
         <v>410</v>
@@ -49191,19 +49191,19 @@
         <v>178</v>
       </c>
       <c r="L221">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="M221">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="N221">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="O221" s="19">
         <v>0</v>
       </c>
       <c r="P221">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q221" t="s">
         <v>410</v>
@@ -49241,10 +49241,10 @@
         <v>89</v>
       </c>
       <c r="L222">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="M222">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="N222">
         <v>2</v>
@@ -49253,7 +49253,7 @@
         <v>2</v>
       </c>
       <c r="P222">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="Q222" t="s">
         <v>410</v>
@@ -49291,10 +49291,10 @@
         <v>89</v>
       </c>
       <c r="L223">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="M223">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="N223">
         <v>2</v>
@@ -49303,7 +49303,7 @@
         <v>2</v>
       </c>
       <c r="P223">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="Q223" t="s">
         <v>410</v>
@@ -49341,19 +49341,19 @@
         <v>89</v>
       </c>
       <c r="L224">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M224">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="N224">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O224" s="19">
         <v>2</v>
       </c>
       <c r="P224">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Q224" t="s">
         <v>410</v>
@@ -49394,10 +49394,10 @@
         <v>5</v>
       </c>
       <c r="M225">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="N225">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O225" s="19">
         <v>0</v>
@@ -49441,19 +49441,19 @@
         <v>89</v>
       </c>
       <c r="L226">
-        <v>30</v>
+        <v>26.5</v>
       </c>
       <c r="M226">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="N226">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O226" s="19">
         <v>0</v>
       </c>
       <c r="P226">
-        <v>30</v>
+        <v>26.5</v>
       </c>
       <c r="Q226" t="s">
         <v>410</v>
@@ -51141,10 +51141,10 @@
         <v>54</v>
       </c>
       <c r="E18">
-        <v>21.364</v>
+        <v>24.82</v>
       </c>
       <c r="F18">
-        <v>355</v>
+        <v>297.5</v>
       </c>
       <c r="H18" t="s">
         <v>85</v>
@@ -51171,10 +51171,10 @@
         <v>54</v>
       </c>
       <c r="P18">
-        <v>59.2</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="Q18">
-        <v>794</v>
+        <v>693.5</v>
       </c>
     </row>
     <row r="19" spans="1:17">
@@ -51191,10 +51191,10 @@
         <v>22</v>
       </c>
       <c r="E19">
-        <v>16.71666666666667</v>
+        <v>17.38</v>
       </c>
       <c r="F19">
-        <v>166</v>
+        <v>116</v>
       </c>
       <c r="H19" t="s">
         <v>86</v>
@@ -51221,10 +51221,10 @@
         <v>83</v>
       </c>
       <c r="P19">
-        <v>24.18416666666667</v>
+        <v>27.0375</v>
       </c>
       <c r="Q19">
-        <v>966</v>
+        <v>788.5</v>
       </c>
     </row>
     <row r="20" spans="1:17">
@@ -51241,10 +51241,10 @@
         <v>46</v>
       </c>
       <c r="E20">
-        <v>51.634</v>
+        <v>53.536</v>
       </c>
       <c r="F20">
-        <v>865</v>
+        <v>699.5</v>
       </c>
     </row>
     <row r="21" spans="1:17">
@@ -51261,10 +51261,10 @@
         <v>15</v>
       </c>
       <c r="E21">
-        <v>37.29</v>
+        <v>47.49666666666666</v>
       </c>
       <c r="F21">
-        <v>374</v>
+        <v>369</v>
       </c>
     </row>
     <row r="25" spans="1:17">
@@ -51285,24 +51285,24 @@
     </row>
     <row r="27" spans="1:17">
       <c r="A27" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B27">
         <v>100</v>
       </c>
       <c r="C27">
-        <v>336</v>
+        <v>270</v>
       </c>
     </row>
     <row r="28" spans="1:17">
       <c r="A28" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B28">
-        <v>96.44</v>
+        <v>98.39</v>
       </c>
       <c r="C28">
-        <v>324</v>
+        <v>265.5</v>
       </c>
     </row>
     <row r="29" spans="1:17">
@@ -51310,10 +51310,10 @@
         <v>61</v>
       </c>
       <c r="B29">
-        <v>59.05</v>
+        <v>73.20999999999999</v>
       </c>
       <c r="C29">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="30" spans="1:17">
@@ -51321,10 +51321,10 @@
         <v>62</v>
       </c>
       <c r="B30">
-        <v>49.85</v>
+        <v>62.32</v>
       </c>
       <c r="C30">
-        <v>167</v>
+        <v>164.5</v>
       </c>
     </row>
     <row r="31" spans="1:17">
@@ -51332,10 +51332,10 @@
         <v>63</v>
       </c>
       <c r="B31">
-        <v>41.25</v>
+        <v>45.36</v>
       </c>
       <c r="C31">
-        <v>138</v>
+        <v>117</v>
       </c>
     </row>
     <row r="32" spans="1:17">
@@ -51343,10 +51343,10 @@
         <v>65</v>
       </c>
       <c r="B32">
-        <v>40.36</v>
+        <v>45.18</v>
       </c>
       <c r="C32">
-        <v>135</v>
+        <v>116.5</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -51354,10 +51354,10 @@
         <v>64</v>
       </c>
       <c r="B33">
-        <v>40.06</v>
+        <v>43.39</v>
       </c>
       <c r="C33">
-        <v>134</v>
+        <v>111.5</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -51365,10 +51365,10 @@
         <v>71</v>
       </c>
       <c r="B34">
-        <v>29.67</v>
+        <v>33.39</v>
       </c>
       <c r="C34">
-        <v>99</v>
+        <v>83.5</v>
       </c>
     </row>
     <row r="68" spans="1:1">
@@ -51554,24 +51554,24 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B24">
         <v>100</v>
       </c>
       <c r="C24">
-        <v>336</v>
+        <v>270</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B25">
-        <v>96.44</v>
+        <v>98.39</v>
       </c>
       <c r="C25">
-        <v>324</v>
+        <v>265.5</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -51579,10 +51579,10 @@
         <v>61</v>
       </c>
       <c r="B26">
-        <v>59.05</v>
+        <v>73.20999999999999</v>
       </c>
       <c r="C26">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -51590,10 +51590,10 @@
         <v>62</v>
       </c>
       <c r="B27">
-        <v>49.85</v>
+        <v>62.32</v>
       </c>
       <c r="C27">
-        <v>167</v>
+        <v>164.5</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -51601,10 +51601,10 @@
         <v>63</v>
       </c>
       <c r="B28">
-        <v>41.25</v>
+        <v>45.36</v>
       </c>
       <c r="C28">
-        <v>138</v>
+        <v>117</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -51612,10 +51612,10 @@
         <v>65</v>
       </c>
       <c r="B29">
-        <v>40.36</v>
+        <v>45.18</v>
       </c>
       <c r="C29">
-        <v>135</v>
+        <v>116.5</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -51623,10 +51623,10 @@
         <v>64</v>
       </c>
       <c r="B30">
-        <v>40.06</v>
+        <v>43.39</v>
       </c>
       <c r="C30">
-        <v>134</v>
+        <v>111.5</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -51634,10 +51634,10 @@
         <v>71</v>
       </c>
       <c r="B31">
-        <v>29.67</v>
+        <v>33.39</v>
       </c>
       <c r="C31">
-        <v>99</v>
+        <v>83.5</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -51674,10 +51674,10 @@
         <v>54</v>
       </c>
       <c r="E35">
-        <v>21.364</v>
+        <v>24.82</v>
       </c>
       <c r="F35">
-        <v>355</v>
+        <v>297.5</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -51694,10 +51694,10 @@
         <v>22</v>
       </c>
       <c r="E36">
-        <v>16.71666666666667</v>
+        <v>17.38</v>
       </c>
       <c r="F36">
-        <v>166</v>
+        <v>116</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -51714,10 +51714,10 @@
         <v>46</v>
       </c>
       <c r="E37">
-        <v>51.634</v>
+        <v>53.536</v>
       </c>
       <c r="F37">
-        <v>865</v>
+        <v>699.5</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -51734,10 +51734,10 @@
         <v>15</v>
       </c>
       <c r="E38">
-        <v>37.29</v>
+        <v>47.49666666666666</v>
       </c>
       <c r="F38">
-        <v>374</v>
+        <v>369</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -51774,10 +51774,10 @@
         <v>130</v>
       </c>
       <c r="E42">
-        <v>32.44333333333334</v>
+        <v>36.082</v>
       </c>
       <c r="F42">
-        <v>1625</v>
+        <v>1365.5</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -51794,10 +51794,10 @@
         <v>7</v>
       </c>
       <c r="E43">
-        <v>40.36</v>
+        <v>45.18</v>
       </c>
       <c r="F43">
-        <v>135</v>
+        <v>116.5</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -51834,10 +51834,10 @@
         <v>54</v>
       </c>
       <c r="E47">
-        <v>59.2</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="F47">
-        <v>794</v>
+        <v>693.5</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -51854,10 +51854,10 @@
         <v>83</v>
       </c>
       <c r="E48">
-        <v>24.18416666666667</v>
+        <v>27.0375</v>
       </c>
       <c r="F48">
-        <v>966</v>
+        <v>788.5</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -55831,19 +55831,19 @@
         <v>14</v>
       </c>
       <c r="AV2">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="AW2">
-        <v>138</v>
+        <v>117</v>
       </c>
       <c r="AX2">
-        <v>9.857143000000001</v>
+        <v>8.357143000000001</v>
       </c>
       <c r="AY2">
-        <v>9.857143000000001</v>
+        <v>8.357143000000001</v>
       </c>
       <c r="AZ2">
-        <v>41.25</v>
+        <v>45.36</v>
       </c>
       <c r="BI2" t="s">
         <v>109</v>
@@ -56008,7 +56008,7 @@
         <v>1</v>
       </c>
       <c r="EC2">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="EP2" t="s">
         <v>110</v>
@@ -56187,19 +56187,19 @@
         <v>16</v>
       </c>
       <c r="AV3">
-        <v>33</v>
+        <v>5.5</v>
       </c>
       <c r="AW3">
-        <v>33</v>
+        <v>5.5</v>
       </c>
       <c r="AX3">
-        <v>2.0625</v>
+        <v>0.34375</v>
       </c>
       <c r="AY3">
-        <v>2.0625</v>
+        <v>0.34375</v>
       </c>
       <c r="AZ3">
-        <v>10.09</v>
+        <v>5.54</v>
       </c>
       <c r="BI3" t="s">
         <v>110</v>
@@ -56552,19 +56552,19 @@
         <v>16</v>
       </c>
       <c r="AV4">
-        <v>324</v>
+        <v>270</v>
       </c>
       <c r="AW4">
-        <v>324</v>
+        <v>270</v>
       </c>
       <c r="AX4">
-        <v>20.25</v>
+        <v>16.875</v>
       </c>
       <c r="AY4">
-        <v>20.25</v>
+        <v>16.875</v>
       </c>
       <c r="AZ4">
-        <v>96.44</v>
+        <v>100</v>
       </c>
       <c r="BI4" t="s">
         <v>111</v>
@@ -56723,7 +56723,7 @@
         <v>1</v>
       </c>
       <c r="EC4">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="EP4" t="s">
         <v>110</v>
@@ -56896,19 +56896,19 @@
         <v>1</v>
       </c>
       <c r="AV5">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="AW5">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="AX5">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="AY5">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="AZ5">
-        <v>2.97</v>
+        <v>6.96</v>
       </c>
       <c r="DL5" t="s">
         <v>59</v>
@@ -56944,7 +56944,7 @@
         <v>2</v>
       </c>
       <c r="EC5">
-        <v>26</v>
+        <v>20.5</v>
       </c>
       <c r="EP5" t="s">
         <v>111</v>
@@ -57117,19 +57117,19 @@
         <v>15</v>
       </c>
       <c r="AV6">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="AW6">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="AX6">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="AY6">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="AZ6">
-        <v>59.05</v>
+        <v>73.20999999999999</v>
       </c>
       <c r="DL6" t="s">
         <v>71</v>
@@ -57323,19 +57323,19 @@
         <v>16</v>
       </c>
       <c r="AV7">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="AW7">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="AX7">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="AY7">
-        <v>4.25</v>
+        <v>3.5</v>
       </c>
       <c r="AZ7">
-        <v>20.47</v>
+        <v>23.57</v>
       </c>
       <c r="DL7" t="s">
         <v>63</v>
@@ -57371,7 +57371,7 @@
         <v>1</v>
       </c>
       <c r="EC7">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="EP7" t="s">
         <v>111</v>
@@ -57538,19 +57538,19 @@
         <v>15</v>
       </c>
       <c r="AV8">
-        <v>135</v>
+        <v>116.5</v>
       </c>
       <c r="AW8">
-        <v>135</v>
+        <v>116.5</v>
       </c>
       <c r="AX8">
-        <v>9</v>
+        <v>7.766667</v>
       </c>
       <c r="AY8">
-        <v>9</v>
+        <v>7.766667</v>
       </c>
       <c r="AZ8">
-        <v>40.36</v>
+        <v>45.18</v>
       </c>
       <c r="DL8" t="s">
         <v>60</v>
@@ -57577,7 +57577,7 @@
         <v>3</v>
       </c>
       <c r="EC8">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="EP8" t="s">
         <v>110</v>
@@ -57759,19 +57759,19 @@
         <v>15</v>
       </c>
       <c r="AV9">
-        <v>134</v>
+        <v>111.5</v>
       </c>
       <c r="AW9">
-        <v>134</v>
+        <v>111.5</v>
       </c>
       <c r="AX9">
-        <v>8.933332999999999</v>
+        <v>7.433333</v>
       </c>
       <c r="AY9">
-        <v>8.933332999999999</v>
+        <v>7.433333</v>
       </c>
       <c r="AZ9">
-        <v>40.06</v>
+        <v>43.39</v>
       </c>
       <c r="DL9" t="s">
         <v>62</v>
@@ -57807,7 +57807,7 @@
         <v>3</v>
       </c>
       <c r="EC9">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="EP9" t="s">
         <v>111</v>
@@ -57986,7 +57986,7 @@
         <v>0</v>
       </c>
       <c r="AZ10">
-        <v>0.3</v>
+        <v>3.57</v>
       </c>
       <c r="DL10" t="s">
         <v>69</v>
@@ -58013,7 +58013,7 @@
         <v>1</v>
       </c>
       <c r="EC10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="EP10" t="s">
         <v>110</v>
@@ -58189,19 +58189,19 @@
         <v>13</v>
       </c>
       <c r="AV11">
-        <v>99</v>
+        <v>83.5</v>
       </c>
       <c r="AW11">
-        <v>99</v>
+        <v>83.5</v>
       </c>
       <c r="AX11">
-        <v>7.615385</v>
+        <v>6.423077</v>
       </c>
       <c r="AY11">
-        <v>7.615385</v>
+        <v>6.423077</v>
       </c>
       <c r="AZ11">
-        <v>29.67</v>
+        <v>33.39</v>
       </c>
       <c r="DL11" t="s">
         <v>65</v>
@@ -58237,7 +58237,7 @@
         <v>1</v>
       </c>
       <c r="EC11">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="EP11" t="s">
         <v>111</v>
@@ -58410,16 +58410,16 @@
         <v>10</v>
       </c>
       <c r="AV12">
+        <v>-10</v>
+      </c>
+      <c r="AW12">
+        <v>-10</v>
+      </c>
+      <c r="AX12">
         <v>-1</v>
       </c>
-      <c r="AW12">
+      <c r="AY12">
         <v>-1</v>
-      </c>
-      <c r="AX12">
-        <v>-0.1</v>
-      </c>
-      <c r="AY12">
-        <v>-0.1</v>
       </c>
       <c r="AZ12">
         <v>0</v>
@@ -58449,7 +58449,7 @@
         <v>1</v>
       </c>
       <c r="EC12">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="EP12" t="s">
         <v>110</v>
@@ -58625,19 +58625,19 @@
         <v>14</v>
       </c>
       <c r="AV13">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="AW13">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="AX13">
-        <v>4.785714</v>
+        <v>3.357143</v>
       </c>
       <c r="AY13">
-        <v>4.785714</v>
+        <v>3.357143</v>
       </c>
       <c r="AZ13">
-        <v>20.18</v>
+        <v>20.36</v>
       </c>
       <c r="DL13" t="s">
         <v>66</v>
@@ -58658,7 +58658,7 @@
         <v>1</v>
       </c>
       <c r="EC13">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="EP13" t="s">
         <v>111</v>
@@ -58831,7 +58831,7 @@
         <v>-1</v>
       </c>
       <c r="AZ14">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="DL14" t="s">
         <v>129</v>
@@ -58864,7 +58864,7 @@
         <v>2</v>
       </c>
       <c r="EC14">
-        <v>-1</v>
+        <v>-1.5</v>
       </c>
       <c r="EP14" t="s">
         <v>111</v>
@@ -59037,19 +59037,19 @@
         <v>16</v>
       </c>
       <c r="AV15">
-        <v>54</v>
+        <v>51.5</v>
       </c>
       <c r="AW15">
-        <v>54</v>
+        <v>51.5</v>
       </c>
       <c r="AX15">
-        <v>3.375</v>
+        <v>3.21875</v>
       </c>
       <c r="AY15">
-        <v>3.375</v>
+        <v>3.21875</v>
       </c>
       <c r="AZ15">
-        <v>16.32</v>
+        <v>21.96</v>
       </c>
       <c r="DL15" t="s">
         <v>64</v>
@@ -59082,7 +59082,7 @@
         <v>2</v>
       </c>
       <c r="EC15">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="EP15" t="s">
         <v>109</v>
@@ -59249,19 +59249,19 @@
         <v>15</v>
       </c>
       <c r="AV16">
-        <v>167</v>
+        <v>164.5</v>
       </c>
       <c r="AW16">
-        <v>167</v>
+        <v>164.5</v>
       </c>
       <c r="AX16">
-        <v>11.133333</v>
+        <v>10.966667</v>
       </c>
       <c r="AY16">
-        <v>11.133333</v>
+        <v>10.966667</v>
       </c>
       <c r="AZ16">
-        <v>49.85</v>
+        <v>62.32</v>
       </c>
       <c r="DL16" t="s">
         <v>61</v>
@@ -59303,7 +59303,7 @@
         <v>1</v>
       </c>
       <c r="EC16">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="EP16" t="s">
         <v>110</v>
@@ -59479,19 +59479,19 @@
         <v>16</v>
       </c>
       <c r="AV17">
-        <v>336</v>
+        <v>265.5</v>
       </c>
       <c r="AW17">
-        <v>336</v>
+        <v>265.5</v>
       </c>
       <c r="AX17">
-        <v>21</v>
+        <v>16.59375</v>
       </c>
       <c r="AY17">
-        <v>21</v>
+        <v>16.59375</v>
       </c>
       <c r="AZ17">
-        <v>100</v>
+        <v>98.39</v>
       </c>
       <c r="DL17" t="s">
         <v>68</v>
@@ -59533,7 +59533,7 @@
         <v>1</v>
       </c>
       <c r="EC17">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="EP17" t="s">
         <v>111</v>
@@ -59628,7 +59628,7 @@
         <v>2</v>
       </c>
       <c r="EC18">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="EP18" t="s">
         <v>111</v>
@@ -59720,7 +59720,7 @@
         <v>3</v>
       </c>
       <c r="EC19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="EP19" t="s">
         <v>109</v>
@@ -59815,7 +59815,7 @@
         <v>2</v>
       </c>
       <c r="EC20">
-        <v>37</v>
+        <v>32.5</v>
       </c>
       <c r="EP20" t="s">
         <v>110</v>
@@ -59892,7 +59892,7 @@
         <v>1</v>
       </c>
       <c r="EC21">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="EP21" t="s">
         <v>111</v>
@@ -59963,7 +59963,7 @@
         <v>1</v>
       </c>
       <c r="EC22">
-        <v>1</v>
+        <v>-4.5</v>
       </c>
       <c r="EP22" t="s">
         <v>110</v>
@@ -60034,7 +60034,7 @@
         <v>2</v>
       </c>
       <c r="EC23">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="EP23" t="s">
         <v>111</v>
@@ -60102,7 +60102,7 @@
         <v>0</v>
       </c>
       <c r="EC24">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="EP24" t="s">
         <v>110</v>
@@ -60167,7 +60167,7 @@
         <v>2</v>
       </c>
       <c r="EC25">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="EP25" t="s">
         <v>111</v>
@@ -60229,7 +60229,7 @@
         <v>1</v>
       </c>
       <c r="EC26">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="EP26" t="s">
         <v>109</v>
@@ -60300,7 +60300,7 @@
         <v>2</v>
       </c>
       <c r="EC27">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="EP27" t="s">
         <v>110</v>
@@ -60368,7 +60368,7 @@
         <v>1</v>
       </c>
       <c r="EC28">
-        <v>-3</v>
+        <v>3.5</v>
       </c>
       <c r="EP28" t="s">
         <v>111</v>
@@ -60436,7 +60436,7 @@
         <v>0</v>
       </c>
       <c r="EC29">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="EP29" t="s">
         <v>110</v>
@@ -60510,7 +60510,7 @@
         <v>1</v>
       </c>
       <c r="EC30">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="EP30" t="s">
         <v>111</v>
@@ -60587,7 +60587,7 @@
         <v>1</v>
       </c>
       <c r="EC31">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="EP31" t="s">
         <v>110</v>
@@ -60652,7 +60652,7 @@
         <v>1</v>
       </c>
       <c r="EC32">
-        <v>-4</v>
+        <v>-4.5</v>
       </c>
       <c r="EP32" t="s">
         <v>111</v>
@@ -60732,7 +60732,7 @@
         <v>3</v>
       </c>
       <c r="EC33">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="EP33" t="s">
         <v>110</v>
@@ -60794,7 +60794,7 @@
         <v>2</v>
       </c>
       <c r="EC34">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="EP34" t="s">
         <v>111</v>
@@ -60868,7 +60868,7 @@
         <v>2</v>
       </c>
       <c r="EC35">
-        <v>6</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="36" spans="116:160">
@@ -60897,7 +60897,7 @@
         <v>2</v>
       </c>
       <c r="EC36">
-        <v>7</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="37" spans="116:160">
@@ -60926,7 +60926,7 @@
         <v>1</v>
       </c>
       <c r="EC37">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="38" spans="116:160">
@@ -60961,7 +60961,7 @@
         <v>1</v>
       </c>
       <c r="EC38">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="116:160">
@@ -61025,7 +61025,7 @@
         <v>2</v>
       </c>
       <c r="EC40">
-        <v>3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="41" spans="116:160">
@@ -61066,7 +61066,7 @@
         <v>1</v>
       </c>
       <c r="EC41">
-        <v>11</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="42" spans="116:160">
@@ -61104,7 +61104,7 @@
         <v>2</v>
       </c>
       <c r="EC42">
-        <v>-5</v>
+        <v>-7.5</v>
       </c>
     </row>
     <row r="43" spans="116:160">
@@ -61142,7 +61142,7 @@
         <v>3</v>
       </c>
       <c r="EC43">
-        <v>25</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="44" spans="116:160">
@@ -61177,7 +61177,7 @@
         <v>1</v>
       </c>
       <c r="EC44">
-        <v>-5</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="45" spans="116:160">
@@ -61218,7 +61218,7 @@
         <v>1</v>
       </c>
       <c r="EC45">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="46" spans="116:160">
@@ -61259,7 +61259,7 @@
         <v>1</v>
       </c>
       <c r="EC46">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="47" spans="116:160">
@@ -61300,7 +61300,7 @@
         <v>1</v>
       </c>
       <c r="EC47">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="48" spans="116:160">
@@ -61332,7 +61332,7 @@
         <v>1</v>
       </c>
       <c r="EC48">
-        <v>-6</v>
+        <v>-6.5</v>
       </c>
     </row>
     <row r="49" spans="116:133">
@@ -61370,7 +61370,7 @@
         <v>1</v>
       </c>
       <c r="EC49">
-        <v>6</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="50" spans="116:133">
@@ -61405,7 +61405,7 @@
         <v>1</v>
       </c>
       <c r="EC50">
-        <v>11</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="51" spans="116:133">
@@ -61434,7 +61434,7 @@
         <v>1</v>
       </c>
       <c r="EC51">
-        <v>3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="52" spans="116:133">
@@ -61492,7 +61492,7 @@
         <v>1</v>
       </c>
       <c r="EC53">
-        <v>-10</v>
+        <v>-11</v>
       </c>
     </row>
     <row r="54" spans="116:133">
@@ -61603,7 +61603,7 @@
         <v>3</v>
       </c>
       <c r="EC56">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="57" spans="116:133">
@@ -61647,7 +61647,7 @@
         <v>2</v>
       </c>
       <c r="EC57">
-        <v>6</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="58" spans="116:133">
@@ -61694,7 +61694,7 @@
         <v>1</v>
       </c>
       <c r="EC58">
-        <v>8</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="59" spans="116:133">
@@ -61729,7 +61729,7 @@
         <v>1</v>
       </c>
       <c r="EC59">
-        <v>-4</v>
+        <v>-6.5</v>
       </c>
     </row>
     <row r="60" spans="116:133">
@@ -61805,7 +61805,7 @@
         <v>1</v>
       </c>
       <c r="EC61">
-        <v>-6</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="62" spans="116:133">
@@ -61840,7 +61840,7 @@
         <v>1</v>
       </c>
       <c r="EC62">
-        <v>-3</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="63" spans="116:133">
@@ -61913,7 +61913,7 @@
         <v>1</v>
       </c>
       <c r="EC64">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="65" spans="116:133">
@@ -61954,7 +61954,7 @@
         <v>3</v>
       </c>
       <c r="EC65">
-        <v>-2</v>
+        <v>-4.5</v>
       </c>
     </row>
     <row r="66" spans="116:133">
@@ -62004,7 +62004,7 @@
         <v>1</v>
       </c>
       <c r="EC66">
-        <v>7</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="67" spans="116:133">
@@ -62051,7 +62051,7 @@
         <v>2</v>
       </c>
       <c r="EC67">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68" spans="116:133">
@@ -62086,7 +62086,7 @@
         <v>2</v>
       </c>
       <c r="EC68">
-        <v>-2</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="69" spans="116:133">
@@ -62130,7 +62130,7 @@
         <v>2</v>
       </c>
       <c r="EC69">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="70" spans="116:133">
@@ -62162,7 +62162,7 @@
         <v>1</v>
       </c>
       <c r="EC70">
-        <v>-3</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="71" spans="116:133">
@@ -62241,7 +62241,7 @@
         <v>1</v>
       </c>
       <c r="EC72">
-        <v>12</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="73" spans="116:133">
@@ -62273,7 +62273,7 @@
         <v>1</v>
       </c>
       <c r="EC73">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="74" spans="116:133">
@@ -62308,7 +62308,7 @@
         <v>2</v>
       </c>
       <c r="EC74">
-        <v>2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="75" spans="116:133">
@@ -62378,7 +62378,7 @@
         <v>2</v>
       </c>
       <c r="EC76">
-        <v>9</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="77" spans="116:133">
@@ -62422,7 +62422,7 @@
         <v>1</v>
       </c>
       <c r="EC77">
-        <v>19</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="78" spans="116:133">
@@ -62463,7 +62463,7 @@
         <v>2</v>
       </c>
       <c r="EC78">
-        <v>18</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="79" spans="116:133">
@@ -62501,7 +62501,7 @@
         <v>2</v>
       </c>
       <c r="EC79">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="80" spans="116:133">
@@ -62536,7 +62536,7 @@
         <v>1</v>
       </c>
       <c r="EC80">
-        <v>20</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="81" spans="116:133">
@@ -62577,7 +62577,7 @@
         <v>1</v>
       </c>
       <c r="EC81">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="82" spans="116:133">
@@ -62621,7 +62621,7 @@
         <v>2</v>
       </c>
       <c r="EC82">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="83" spans="116:133">
@@ -62676,7 +62676,7 @@
         <v>1</v>
       </c>
       <c r="EC84">
-        <v>-4</v>
+        <v>-4.5</v>
       </c>
     </row>
     <row r="85" spans="116:133">
@@ -62731,7 +62731,7 @@
         <v>1</v>
       </c>
       <c r="EC86">
-        <v>-1</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="87" spans="116:133">
@@ -62763,7 +62763,7 @@
         <v>1</v>
       </c>
       <c r="EC87">
-        <v>11</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="88" spans="116:133">
@@ -62804,7 +62804,7 @@
         <v>1</v>
       </c>
       <c r="EC88">
-        <v>14</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="89" spans="116:133">
@@ -62842,7 +62842,7 @@
         <v>1</v>
       </c>
       <c r="EC89">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="90" spans="116:133">
@@ -62877,7 +62877,7 @@
         <v>1</v>
       </c>
       <c r="EC90">
-        <v>-4</v>
+        <v>-6.5</v>
       </c>
     </row>
     <row r="91" spans="116:133">
@@ -62912,7 +62912,7 @@
         <v>1</v>
       </c>
       <c r="EC91">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="92" spans="116:133">
@@ -62941,7 +62941,7 @@
         <v>1</v>
       </c>
       <c r="EC92">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="93" spans="116:133">
@@ -63026,7 +63026,7 @@
         <v>2</v>
       </c>
       <c r="EC94">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95" spans="116:133">
@@ -63058,7 +63058,7 @@
         <v>1</v>
       </c>
       <c r="EC95">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="96" spans="116:133">
@@ -63087,7 +63087,7 @@
         <v>1</v>
       </c>
       <c r="EC96">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="97" spans="116:133">
@@ -63122,7 +63122,7 @@
         <v>1</v>
       </c>
       <c r="EC97">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="98" spans="116:133">
@@ -63186,7 +63186,7 @@
         <v>2</v>
       </c>
       <c r="EC99">
-        <v>5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="100" spans="116:133">
@@ -63227,7 +63227,7 @@
         <v>1</v>
       </c>
       <c r="EC100">
-        <v>13</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="101" spans="116:133">
@@ -63274,7 +63274,7 @@
         <v>1</v>
       </c>
       <c r="EC101">
-        <v>9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="102" spans="116:133">
@@ -63309,7 +63309,7 @@
         <v>3</v>
       </c>
       <c r="EC102">
-        <v>13</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="103" spans="116:133">
@@ -63362,7 +63362,7 @@
         <v>2</v>
       </c>
       <c r="EC103">
-        <v>14</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="104" spans="116:133">
@@ -63400,7 +63400,7 @@
         <v>1</v>
       </c>
       <c r="EC104">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="105" spans="116:133">
@@ -63438,7 +63438,7 @@
         <v>1</v>
       </c>
       <c r="EC105">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="106" spans="116:133">
@@ -63511,7 +63511,7 @@
         <v>1</v>
       </c>
       <c r="EC107">
-        <v>14</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="108" spans="116:133">
@@ -63546,7 +63546,7 @@
         <v>1</v>
       </c>
       <c r="EC108">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="109" spans="116:133">
@@ -63587,7 +63587,7 @@
         <v>1</v>
       </c>
       <c r="EC109">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="110" spans="116:133">
@@ -63619,7 +63619,7 @@
         <v>1</v>
       </c>
       <c r="EC110">
-        <v>-1</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="111" spans="116:133">
@@ -63657,7 +63657,7 @@
         <v>1</v>
       </c>
       <c r="EC111">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112" spans="116:133">
@@ -63698,7 +63698,7 @@
         <v>1</v>
       </c>
       <c r="EC112">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="113" spans="116:133">
@@ -63739,7 +63739,7 @@
         <v>1</v>
       </c>
       <c r="EC113">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="114" spans="116:133">
@@ -63812,7 +63812,7 @@
         <v>1</v>
       </c>
       <c r="EC115">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="116" spans="116:133">
@@ -63847,7 +63847,7 @@
         <v>2</v>
       </c>
       <c r="EC116">
-        <v>-4</v>
+        <v>-6.5</v>
       </c>
     </row>
     <row r="117" spans="116:133">
@@ -63885,7 +63885,7 @@
         <v>2</v>
       </c>
       <c r="EC117">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="118" spans="116:133">
@@ -63920,7 +63920,7 @@
         <v>2</v>
       </c>
       <c r="EC118">
-        <v>19</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="119" spans="116:133">
@@ -63961,7 +63961,7 @@
         <v>2</v>
       </c>
       <c r="EC119">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="120" spans="116:133">
@@ -63990,7 +63990,7 @@
         <v>1</v>
       </c>
       <c r="EC120">
-        <v>3</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="121" spans="116:133">
@@ -64019,7 +64019,7 @@
         <v>1</v>
       </c>
       <c r="EC121">
-        <v>-1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="122" spans="116:133">
@@ -64054,7 +64054,7 @@
         <v>1</v>
       </c>
       <c r="EC122">
-        <v>7</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="123" spans="116:133">
@@ -64124,7 +64124,7 @@
         <v>2</v>
       </c>
       <c r="EC124">
-        <v>27</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="125" spans="116:133">
@@ -64171,7 +64171,7 @@
         <v>1</v>
       </c>
       <c r="EC125">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="126" spans="116:133">
@@ -64206,7 +64206,7 @@
         <v>2</v>
       </c>
       <c r="EC126">
-        <v>2</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="127" spans="116:133">
@@ -64247,7 +64247,7 @@
         <v>1</v>
       </c>
       <c r="EC127">
-        <v>9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="128" spans="116:133">
@@ -64288,7 +64288,7 @@
         <v>3</v>
       </c>
       <c r="EC128">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="129" spans="116:133">
@@ -64320,7 +64320,7 @@
         <v>0.5</v>
       </c>
       <c r="EC129">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="130" spans="116:133">
@@ -64358,7 +64358,7 @@
         <v>1</v>
       </c>
       <c r="EC130">
-        <v>39</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="131" spans="116:133">
@@ -64402,7 +64402,7 @@
         <v>1</v>
       </c>
       <c r="EC131">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="132" spans="116:133">
@@ -64440,7 +64440,7 @@
         <v>1</v>
       </c>
       <c r="EC132">
-        <v>5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="133" spans="116:133">
@@ -64472,7 +64472,7 @@
         <v>1</v>
       </c>
       <c r="EC133">
-        <v>10</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="134" spans="116:133">
@@ -64501,7 +64501,7 @@
         <v>0</v>
       </c>
       <c r="EC134">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135" spans="116:133">
@@ -64539,7 +64539,7 @@
         <v>1</v>
       </c>
       <c r="EC135">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136" spans="116:133">
@@ -64580,7 +64580,7 @@
         <v>3</v>
       </c>
       <c r="EC136">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="137" spans="116:133">
@@ -64618,7 +64618,7 @@
         <v>1</v>
       </c>
       <c r="EC137">
-        <v>23</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="138" spans="116:133">
@@ -64650,7 +64650,7 @@
         <v>1</v>
       </c>
       <c r="EC138">
-        <v>6</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="139" spans="116:133">
@@ -64688,7 +64688,7 @@
         <v>1</v>
       </c>
       <c r="EC139">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="140" spans="116:133">
@@ -64723,7 +64723,7 @@
         <v>2</v>
       </c>
       <c r="EC140">
-        <v>23</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="141" spans="116:133">
@@ -64764,7 +64764,7 @@
         <v>1</v>
       </c>
       <c r="EC141">
-        <v>15</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="142" spans="116:133">
@@ -64796,7 +64796,7 @@
         <v>0.333333</v>
       </c>
       <c r="EC142">
-        <v>20</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="143" spans="116:133">
@@ -64843,7 +64843,7 @@
         <v>1</v>
       </c>
       <c r="EC143">
-        <v>28</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="144" spans="116:133">
@@ -64881,7 +64881,7 @@
         <v>2</v>
       </c>
       <c r="EC144">
-        <v>3</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="145" spans="116:133">
@@ -64919,7 +64919,7 @@
         <v>1</v>
       </c>
       <c r="EC145">
-        <v>17</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="146" spans="116:133">
@@ -64960,7 +64960,7 @@
         <v>1</v>
       </c>
       <c r="EC146">
-        <v>6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="147" spans="116:133">
@@ -64992,7 +64992,7 @@
         <v>3</v>
       </c>
       <c r="EC147">
-        <v>1</v>
+        <v>-4.5</v>
       </c>
     </row>
     <row r="148" spans="116:133">
@@ -65042,7 +65042,7 @@
         <v>1</v>
       </c>
       <c r="EC148">
-        <v>11</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="149" spans="116:133">
@@ -65083,7 +65083,7 @@
         <v>1</v>
       </c>
       <c r="EC149">
-        <v>17</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="150" spans="116:133">
@@ -65115,7 +65115,7 @@
         <v>1</v>
       </c>
       <c r="EC150">
-        <v>5</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="151" spans="116:133">
@@ -65162,7 +65162,7 @@
         <v>1</v>
       </c>
       <c r="EC151">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="152" spans="116:133">
@@ -65206,7 +65206,7 @@
         <v>1</v>
       </c>
       <c r="EC152">
-        <v>10</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="153" spans="116:133">
@@ -65241,7 +65241,7 @@
         <v>1</v>
       </c>
       <c r="EC153">
-        <v>39</v>
+        <v>32</v>
       </c>
     </row>
     <row r="154" spans="116:133">
@@ -65282,7 +65282,7 @@
         <v>2</v>
       </c>
       <c r="EC154">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="155" spans="116:133">
@@ -65314,7 +65314,7 @@
         <v>1</v>
       </c>
       <c r="EC155">
-        <v>-7</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="156" spans="116:133">
@@ -65387,7 +65387,7 @@
         <v>1</v>
       </c>
       <c r="EC157">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="158" spans="116:133">
@@ -65419,7 +65419,7 @@
         <v>1</v>
       </c>
       <c r="EC158">
-        <v>17</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="159" spans="116:133">
@@ -65486,7 +65486,7 @@
         <v>3</v>
       </c>
       <c r="EC160">
-        <v>-2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="161" spans="116:133">
@@ -65521,7 +65521,7 @@
         <v>1</v>
       </c>
       <c r="EC161">
-        <v>-1</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="162" spans="116:133">
@@ -65562,7 +65562,7 @@
         <v>1</v>
       </c>
       <c r="EC162">
-        <v>22</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="163" spans="116:133">
@@ -65597,7 +65597,7 @@
         <v>1</v>
       </c>
       <c r="EC163">
-        <v>11</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="164" spans="116:133">
@@ -65632,7 +65632,7 @@
         <v>1</v>
       </c>
       <c r="EC164">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="165" spans="116:133">
@@ -65670,7 +65670,7 @@
         <v>3</v>
       </c>
       <c r="EC165">
-        <v>35</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="166" spans="116:133">
@@ -65708,7 +65708,7 @@
         <v>1</v>
       </c>
       <c r="EC166">
-        <v>22</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="167" spans="116:133">
@@ -65749,7 +65749,7 @@
         <v>2</v>
       </c>
       <c r="EC167">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="168" spans="116:133">
@@ -65787,7 +65787,7 @@
         <v>2</v>
       </c>
       <c r="EC168">
-        <v>3</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="169" spans="116:133">
@@ -65816,7 +65816,7 @@
         <v>0</v>
       </c>
       <c r="EC169">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="170" spans="116:133">
@@ -65944,7 +65944,7 @@
         <v>1</v>
       </c>
       <c r="EC173">
-        <v>20</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="174" spans="116:133">
@@ -65982,7 +65982,7 @@
         <v>1</v>
       </c>
       <c r="EC174">
-        <v>0</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="175" spans="116:133">
@@ -66017,7 +66017,7 @@
         <v>2</v>
       </c>
       <c r="EC175">
-        <v>27</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="176" spans="116:133">
@@ -66058,7 +66058,7 @@
         <v>1</v>
       </c>
       <c r="EC176">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="177" spans="116:133">
@@ -66096,7 +66096,7 @@
         <v>2</v>
       </c>
       <c r="EC177">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="178" spans="116:133">
@@ -66134,7 +66134,7 @@
         <v>1</v>
       </c>
       <c r="EC178">
-        <v>45</v>
+        <v>39.5</v>
       </c>
     </row>
     <row r="179" spans="116:133">
@@ -66169,7 +66169,7 @@
         <v>1</v>
       </c>
       <c r="EC179">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="180" spans="116:133">
@@ -66204,7 +66204,7 @@
         <v>1</v>
       </c>
       <c r="EC180">
-        <v>9</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="181" spans="116:133">
@@ -66233,7 +66233,7 @@
         <v>1</v>
       </c>
       <c r="EC181">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="182" spans="116:133">
@@ -66265,7 +66265,7 @@
         <v>1</v>
       </c>
       <c r="EC182">
-        <v>9</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="183" spans="116:133">
@@ -66329,7 +66329,7 @@
         <v>1</v>
       </c>
       <c r="EC184">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="185" spans="116:133">
@@ -66402,7 +66402,7 @@
         <v>2</v>
       </c>
       <c r="EC186">
-        <v>7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="187" spans="116:133">
@@ -66440,7 +66440,7 @@
         <v>1</v>
       </c>
       <c r="EC187">
-        <v>30</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="188" spans="116:133">
@@ -66478,7 +66478,7 @@
         <v>1</v>
       </c>
       <c r="EC188">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="189" spans="116:133">
@@ -66525,7 +66525,7 @@
         <v>1</v>
       </c>
       <c r="EC189">
-        <v>18</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="190" spans="116:133">
@@ -66569,7 +66569,7 @@
         <v>1</v>
       </c>
       <c r="EC190">
-        <v>25</v>
+        <v>20.5</v>
       </c>
     </row>
     <row r="191" spans="116:133">
@@ -66648,7 +66648,7 @@
         <v>1</v>
       </c>
       <c r="EC192">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="193" spans="116:133">
@@ -66692,7 +66692,7 @@
         <v>1</v>
       </c>
       <c r="EC193">
-        <v>7</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="194" spans="116:133">
@@ -66736,7 +66736,7 @@
         <v>1</v>
       </c>
       <c r="EC194">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="195" spans="116:133">
@@ -66771,7 +66771,7 @@
         <v>1</v>
       </c>
       <c r="EC195">
-        <v>4</v>
+        <v>3.5</v>
       </c>
     </row>
   </sheetData>
